--- a/miner snapshots.xlsx
+++ b/miner snapshots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prestonacosta/Desktop/Hunter Holdings /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752A9FA0-8224-7340-B7C7-C1737BAE00D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C73F4A7-6F71-154A-B039-E6B366BDA2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20200" activeTab="7" xr2:uid="{0E1CF479-6F43-7441-A168-C06CD1A60F93}"/>
   </bookViews>
@@ -233,7 +233,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="174">
   <si>
     <t>miner value (EH/s)</t>
   </si>
@@ -712,38 +712,7 @@
     <t>EH/s by H1 2025</t>
   </si>
   <si>
-    <t>EH/s by H2 2025</t>
-  </si>
-  <si>
     <t>salvage ratio per share</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> shares outstanding</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Implied</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Financial Metrics </t>
-    </r>
-  </si>
-  <si>
-    <t>Implied salvage ratio per share</t>
   </si>
   <si>
     <t>Value</t>
@@ -784,6 +753,9 @@
   <si>
     <t>50 mw of operational</t>
   </si>
+  <si>
+    <t>MW opperational</t>
+  </si>
 </sst>
 </file>
 
@@ -804,7 +776,7 @@
     <numFmt numFmtId="173" formatCode="0.0%"/>
     <numFmt numFmtId="174" formatCode="_([$$-409]* #,##0.000_);_([$$-409]* \(#,##0.000\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -942,12 +914,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri (Body)"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1115,9 +1081,9 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1273,24 +1239,18 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="16" borderId="0" xfId="12" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="2" fillId="14" borderId="0" xfId="8" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="10" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="18" borderId="0" xfId="13" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="19" fillId="18" borderId="0" xfId="13" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="18" borderId="0" xfId="13" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="10" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="7" applyFont="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="20% - Accent2" xfId="9" builtinId="34"/>
@@ -3167,6 +3127,28 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800"/>
+              <a:t>Energized hashrate EH/S</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3180,12 +3162,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -3217,23 +3196,27 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="34925" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent1"/>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'monthly data'!$A$47:$L$47</c:f>
+              <c:f>'monthly data'!$A$47:$Q$47</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>45292</c:v>
                 </c:pt>
@@ -3270,15 +3253,30 @@
                 <c:pt idx="11">
                   <c:v>45627</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45689</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45778</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'monthly data'!$A$48:$L$48</c:f>
+              <c:f>'monthly data'!$A$48:$Q$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>6.2</c:v>
                 </c:pt>
@@ -3315,6 +3313,21 @@
                 <c:pt idx="11">
                   <c:v>31</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>41</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3333,6 +3346,27 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1"/>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="lt1">
+                      <a:alpha val="0"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
         <c:smooth val="0"/>
         <c:axId val="2143520176"/>
         <c:axId val="2142480720"/>
@@ -3350,12 +3384,9 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3366,12 +3397,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3394,20 +3422,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3424,12 +3438,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3464,14 +3475,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="accent1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -3523,12 +3531,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -3600,28 +3605,98 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
-            <a:sp3d>
-              <a:contourClr>
-                <a:schemeClr val="tx1"/>
-              </a:contourClr>
-            </a:sp3d>
+            <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'monthly data'!$A$50:$L$50</c:f>
+              <c:f>'monthly data'!$A$50:$Q$50</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>45292</c:v>
                 </c:pt>
@@ -3658,15 +3733,30 @@
                 <c:pt idx="11">
                   <c:v>45650</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>45681</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45712</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45740</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45771</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45801</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'monthly data'!$A$51:$L$51</c:f>
+              <c:f>'monthly data'!$A$51:$Q$51</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>2.5</c:v>
                 </c:pt>
@@ -3703,6 +3793,21 @@
                 <c:pt idx="11">
                   <c:v>1.6</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.6</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3714,7 +3819,7 @@
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -3739,8 +3844,14 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3749,12 +3860,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3781,7 +3889,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="tx2">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -3807,12 +3915,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3851,7 +3956,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="tx2">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -3906,12 +4011,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -3943,23 +4045,27 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="34925" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent1"/>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'monthly data'!$A$53:$L$53</c:f>
+              <c:f>'monthly data'!$A$53:$Q$53</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>45292</c:v>
                 </c:pt>
@@ -3996,15 +4102,30 @@
                 <c:pt idx="11">
                   <c:v>45650</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>45681</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45712</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45740</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45771</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45801</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'monthly data'!$A$54:$L$54</c:f>
+              <c:f>'monthly data'!$A$54:$Q$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>60.4</c:v>
                 </c:pt>
@@ -4041,6 +4162,21 @@
                 <c:pt idx="11">
                   <c:v>18.8</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16.3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4059,6 +4195,27 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1"/>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="lt1">
+                      <a:alpha val="0"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
         <c:smooth val="0"/>
         <c:axId val="8236031"/>
         <c:axId val="7546159"/>
@@ -4076,8 +4233,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -4086,12 +4246,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4114,20 +4271,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -4144,12 +4287,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4184,14 +4324,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="accent1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -16099,33 +16236,556 @@
 </file>
 
 <file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="229">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="100" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="290">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -16140,7 +16800,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -16148,7 +16808,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -16156,17 +16816,14 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
@@ -16175,9 +16832,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
@@ -16200,45 +16856,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="31750" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -16247,36 +16893,32 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="12700">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt2"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -16292,21 +16934,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -16340,17 +16977,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -16359,14 +16996,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -16378,26 +17014,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -16411,96 +17041,99 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -16508,17 +17141,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -16527,12 +17160,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -16541,14 +17171,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -16557,10 +17187,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
@@ -16569,7 +17196,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -16590,10 +17217,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -16602,61 +17226,60 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="229">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="100" baseline="0"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -16668,22 +17291,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -16691,10 +17310,7 @@
       </a:solidFill>
       <a:ln>
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -16705,58 +17321,87 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
@@ -16765,10 +17410,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -16780,51 +17425,49 @@
     </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -16833,37 +17476,51 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
   <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:errorBar>
   <cs:floor>
@@ -16871,28 +17528,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -16900,59 +17552,62 @@
     </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -16961,615 +17616,128 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -17578,10 +17746,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -17590,14 +17755,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -38915,7 +39074,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{C4498FB8-3B81-904F-8674-42E2E05280E2}" type="pres">
-      <dgm:prSet presAssocID="{EB8CE5AD-3BF5-2A49-AEFE-B84A408CC38C}" presName="box" presStyleLbl="node1" presStyleIdx="0" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{EB8CE5AD-3BF5-2A49-AEFE-B84A408CC38C}" presName="box" presStyleLbl="node1" presStyleIdx="0" presStyleCnt="5" custLinFactNeighborX="135" custLinFactNeighborY="2800"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{B7F7C2B0-8508-D245-8EE0-CF58B9404105}" type="pres">
@@ -38953,7 +39112,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{F6C01A38-DB88-FF4C-8099-8D07A3FFAC70}" type="pres">
-      <dgm:prSet presAssocID="{EB5243B5-5BB6-624A-85D7-1442DDFCBFD5}" presName="box" presStyleLbl="node1" presStyleIdx="1" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{EB5243B5-5BB6-624A-85D7-1442DDFCBFD5}" presName="box" presStyleLbl="node1" presStyleIdx="1" presStyleCnt="5" custLinFactNeighborY="1867"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{F517E9F2-DE06-F44E-8FFC-E33AF7C61F6C}" type="pres">
@@ -43255,8 +43414,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="10750550" cy="1554360"/>
+          <a:off x="0" y="44336"/>
+          <a:ext cx="10801091" cy="1583439"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -43300,12 +43459,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="57150" tIns="57150" rIns="57150" bIns="57150" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="60960" tIns="60960" rIns="60960" bIns="60960" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="666750">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -43318,7 +43477,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1500" kern="1200"/>
+            <a:rPr lang="en-US" sz="1600" kern="1200"/>
             <a:t>Childress, Texas</a:t>
           </a:r>
         </a:p>
@@ -43432,8 +43591,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2305546" y="0"/>
-        <a:ext cx="8445003" cy="1554360"/>
+        <a:off x="2318562" y="44336"/>
+        <a:ext cx="8482528" cy="1583439"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B7F7C2B0-8508-D245-8EE0-CF58B9404105}">
@@ -43443,8 +43602,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="134956" y="136472"/>
-          <a:ext cx="2161699" cy="1287359"/>
+          <a:off x="137767" y="139025"/>
+          <a:ext cx="2171861" cy="1311442"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -43498,8 +43657,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="0" y="1709797"/>
-          <a:ext cx="10750550" cy="1554360"/>
+          <a:off x="0" y="1771345"/>
+          <a:ext cx="10801091" cy="1583439"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -43543,12 +43702,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="57150" tIns="57150" rIns="57150" bIns="57150" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="60960" tIns="60960" rIns="60960" bIns="60960" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="666750">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -43561,7 +43720,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1500" kern="1200"/>
+            <a:rPr lang="en-US" sz="1600" kern="1200"/>
             <a:t>Prince George, British Columbia</a:t>
           </a:r>
         </a:p>
@@ -43675,8 +43834,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2305546" y="1709797"/>
-        <a:ext cx="8445003" cy="1554360"/>
+        <a:off x="2318562" y="1771345"/>
+        <a:ext cx="8482528" cy="1583439"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F517E9F2-DE06-F44E-8FFC-E33AF7C61F6C}">
@@ -43686,8 +43845,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="155436" y="1865233"/>
-          <a:ext cx="2150110" cy="1243488"/>
+          <a:off x="158343" y="1900126"/>
+          <a:ext cx="2160218" cy="1266751"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -43741,8 +43900,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="0" y="3419594"/>
-          <a:ext cx="10750550" cy="1554360"/>
+          <a:off x="0" y="3483566"/>
+          <a:ext cx="10801091" cy="1583439"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -43786,12 +43945,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="57150" tIns="57150" rIns="57150" bIns="57150" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="60960" tIns="60960" rIns="60960" bIns="60960" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="666750">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -43804,7 +43963,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1500" kern="1200"/>
+            <a:rPr lang="en-US" sz="1600" kern="1200"/>
             <a:t>Canal Flats, British Columbia</a:t>
           </a:r>
         </a:p>
@@ -43882,8 +44041,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2305546" y="3419594"/>
-        <a:ext cx="8445003" cy="1554360"/>
+        <a:off x="2318562" y="3483566"/>
+        <a:ext cx="8482528" cy="1583439"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1AB93289-EC83-0543-8185-0E116E2BF8EB}">
@@ -43893,8 +44052,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="155436" y="3575030"/>
-          <a:ext cx="2150110" cy="1243488"/>
+          <a:off x="158343" y="3641909"/>
+          <a:ext cx="2160218" cy="1266751"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -43948,8 +44107,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="0" y="5129391"/>
-          <a:ext cx="10750550" cy="1554360"/>
+          <a:off x="0" y="5225349"/>
+          <a:ext cx="10801091" cy="1583439"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -43993,12 +44152,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="57150" tIns="57150" rIns="57150" bIns="57150" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="60960" tIns="60960" rIns="60960" bIns="60960" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="666750">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -44011,7 +44170,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1500" kern="1200"/>
+            <a:rPr lang="en-US" sz="1600" kern="1200"/>
             <a:t>Mackenzie, British Columbia</a:t>
           </a:r>
         </a:p>
@@ -44089,8 +44248,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2305546" y="5129391"/>
-        <a:ext cx="8445003" cy="1554360"/>
+        <a:off x="2318562" y="5225349"/>
+        <a:ext cx="8482528" cy="1583439"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C0BFC06E-2B90-D945-BF40-EAF839C84716}">
@@ -44100,8 +44259,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="155436" y="5284827"/>
-          <a:ext cx="2150110" cy="1243488"/>
+          <a:off x="158343" y="5383692"/>
+          <a:ext cx="2160218" cy="1266751"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -44155,8 +44314,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="0" y="6839188"/>
-          <a:ext cx="10750550" cy="1692605"/>
+          <a:off x="0" y="6967132"/>
+          <a:ext cx="10801091" cy="1724270"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -44200,12 +44359,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="57150" tIns="57150" rIns="57150" bIns="57150" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="60960" tIns="60960" rIns="60960" bIns="60960" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="666750">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="711200">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -44218,7 +44377,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1500" kern="1200"/>
+            <a:rPr lang="en-US" sz="1600" kern="1200"/>
             <a:t>Pipeline (Sweetwater, TX)</a:t>
           </a:r>
         </a:p>
@@ -44314,8 +44473,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2305546" y="6839188"/>
-        <a:ext cx="8445003" cy="1692605"/>
+        <a:off x="2318562" y="6967132"/>
+        <a:ext cx="8482528" cy="1724270"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AEBEA5FD-4A69-AA4F-8863-797028126976}">
@@ -44325,8 +44484,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="155436" y="7063746"/>
-          <a:ext cx="2150110" cy="1243488"/>
+          <a:off x="158343" y="7195891"/>
+          <a:ext cx="2160218" cy="1266751"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -53925,16 +54084,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>525317</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>19627</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>386770</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>135081</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>109680</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>61191</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>802407</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>176645</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -54666,15 +54825,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>927100</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:colOff>65836</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>15327</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>1722530</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>116782</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -54703,16 +54862,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1092200</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>11971</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>656897</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>116781</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -54741,16 +54900,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>939799</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>706237</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>32657</xdr:rowOff>
+      <xdr:rowOff>18059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>685799</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>140305</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>72988</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>102184</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -55183,38 +55342,38 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>15.92</v>
-    <v>4.1500000000000004</v>
-    <v>1.544</v>
-    <v>0.59</v>
-    <v>4.7503999999999998E-2</v>
-    <v>0.05</v>
-    <v>3.8429999999999996E-3</v>
+    <v>5.125</v>
+    <v>3.7778999999999998</v>
+    <v>-0.13</v>
+    <v>-1.2621E-2</v>
+    <v>-0.09</v>
+    <v>-8.8500000000000002E-3</v>
     <v>USD</v>
-    <v>IREN Limited, formerly Iris Energy Limited, is an Australia-based company, which owns and operates data centers powered by 100% renewable energy. Its facilities are optimized for Bitcoin mining, artificial intelligence (AI) cloud services, and other power-dense compute. Its data center mining facilities are in Canal Flats, Mackenzie, Prince George and Childress. Bitcoin Mining provides security to the Bitcoin network. Al Cloud Services provides cloud compute to Al customers, 1,896 NVIDIA H100 and H200 GPUs. Its Canal Flats facility is in the Canadian Rockies, 100 kilometers (km) from Cranbrook regional airport and 500km east of Vancouver. Its facility is in Prince George, the city in northern British Columbia, located 500 km north of Vancouver. Its facility is located in Childress County, Texas, over 250 miles northwest of Dallas and in close proximity to multiple wind and solar generating facilities in the region. Its Childress operations comprise 200MW of operating data centers.</v>
+    <v>IREN Limited is an Australia-based company, which owns and operates data centers powered by 100% renewable energy. Its facilities are optimized for Bitcoin mining, artificial intelligence (AI) cloud services, and other power-dense compute. Its data center mining facilities are in Canal Flats, Mackenzie, Prince George and Childress. Bitcoin Mining provides security to the Bitcoin network. Al Cloud Services provides cloud compute to Al customers, approximately 1,896 NVIDIA H100 and H200 GPUs. Its Canal Flats facility is in the Canadian Rockies, 100 kilometers (km) from Cranbrook regional airport and 500km east of Vancouver. Its facility is in Prince George, the city in northern British Columbia, located 500 km north of Vancouver. Its facility is located in Childress County, Texas, over 250 miles northwest of Dallas and in close proximity to multiple wind and solar generating facilities in the region. Its Childress operations comprise 200 Mega Watt of operating data centers.</v>
     <v>144</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>Level 6, 55 Market Street, SYDNEY, NEW SOUTH WALES, NSW 2000 AU</v>
-    <v>13.17</v>
+    <v>10.5</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936494652342</v>
+    <v>45820.89038118047</v>
     <v>0</v>
-    <v>11.97</v>
-    <v>2789418157</v>
+    <v>9.9</v>
+    <v>2282747013</v>
     <v>IREN LIMITED</v>
     <v>IREN LIMITED</v>
-    <v>12.02</v>
+    <v>10</v>
     <v>0</v>
-    <v>12.42</v>
-    <v>13.01</v>
-    <v>13.06</v>
-    <v>214405700</v>
+    <v>10.3</v>
+    <v>10.17</v>
+    <v>10.08</v>
+    <v>224458900</v>
     <v>IREN</v>
     <v>IREN LIMITED (XNAS:IREN)</v>
-    <v>13513541</v>
-    <v>16982661</v>
+    <v>13900877</v>
+    <v>17317007</v>
     <v>2018</v>
   </rv>
   <rv s="2">
@@ -55232,20 +55391,20 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>109071.86</v>
-    <v>2.3123</v>
-    <v>173.81</v>
-    <v>1.779E-3</v>
+    <v>111965.62</v>
+    <v>49445.08</v>
+    <v>280.45</v>
+    <v>2.6450000000000002E-3</v>
     <v>USD</v>
     <v>BTC</v>
-    <v>97946.19</v>
+    <v>106358.08</v>
     <v>Currency Pair</v>
-    <v>45700.936354166668</v>
-    <v>97448.12</v>
+    <v>45820.891493055555</v>
+    <v>105954.48</v>
     <v>Bitcoin/US Dollar FX Spot Rate</v>
-    <v>97689.05</v>
-    <v>97683.32</v>
-    <v>97857.13</v>
+    <v>105955.83</v>
+    <v>106013.27</v>
+    <v>106293.72</v>
     <v>BTCUSD</v>
     <v>BTC/USD</v>
   </rv>
@@ -55265,19 +55424,19 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>4108.1000000000004</v>
-    <v>102.5</v>
-    <v>63.14</v>
-    <v>2.3531E-2</v>
+    <v>1387.02</v>
+    <v>10.14</v>
+    <v>3.8369999999999997E-3</v>
     <v>USD</v>
     <v>ETH</v>
-    <v>2757.16</v>
+    <v>2655.56</v>
     <v>Currency Pair</v>
-    <v>45700.936469907407</v>
-    <v>2679.29</v>
+    <v>45820.891400462962</v>
+    <v>2634.13</v>
     <v>Ethereum/US Dollar FX Spot Rate</v>
-    <v>2683.46</v>
-    <v>2683.27</v>
-    <v>2746.41</v>
+    <v>2637.89</v>
+    <v>2642.51</v>
+    <v>2652.65</v>
     <v>ETHUSD</v>
     <v>ETH/USD</v>
   </rv>
@@ -55301,38 +55460,38 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>26.99</v>
-    <v>5.23</v>
-    <v>2.0476999999999999</v>
-    <v>0.5</v>
-    <v>3.1927999999999998E-2</v>
-    <v>7.0000000000000007E-2</v>
-    <v>4.3319999999999999E-3</v>
+    <v>5.4</v>
+    <v>2.3239999999999998</v>
+    <v>-0.54</v>
+    <v>-3.9045999999999997E-2</v>
+    <v>0.15</v>
+    <v>1.1287E-2</v>
     <v>USD</v>
-    <v>Bitdeer Technologies Group is a technology company for blockchain. It provides computing solutions for customers. The Company handles processes involved in computing, such as equipment procurement, transport logistics, datacenter design and construction, and equipment management. It primarily operates three business lines: self-mining, hash rate sharing, and hosting. Its Self-mining refers to cryptocurrency mining for its own account, which allows it to directly capture the high appreciation potential of cryptocurrency. It offers two types of hash rate sharing solutions, namely Cloud Hash Rate and Hash Rate Marketplace. Through Cloud Hash Rate, the Company sells its hash rate to customers. It offers hash rate subscription plans at fixed price and share mining income with them under certain arrangements. The Company's hosting services offer customers one-stop mining rig hosting solutions encompassing deployment, maintenance and management services for efficient cryptocurrency mining.</v>
-    <v>211</v>
+    <v>Bitdeer Technologies Group is a technology company for blockchain. It provides computing solutions for customers. The Company handles processes involved in computing, such as equipment procurement, transport logistics, datacenter design and construction, and equipment management. It primarily operates three business lines, namely self-mining, hash rate sharing, and hosting. Self-mining refers to cryptocurrency mining for its own account, which allows it to directly capture the high appreciation potential of cryptocurrency. It offers two types of hash rate sharing solutions, namely Cloud Hash Rate and Hash Rate Marketplace. Through Cloud Hash Rate, the Company sells its hash rate to customers. It offers hash rate subscription plans at a fixed price and shares mining income with them under certain arrangements. Its hosting services offer customers one-stop mining rig hosting solutions encompassing deployment, maintenance, and management services for efficient cryptocurrency mining.</v>
+    <v>246</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>08 Kallang Avenue, Aperia Tower 1, #09-0, 339509 SG</v>
-    <v>16.510000000000002</v>
+    <v>13.8</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.935675508597</v>
+    <v>45820.888790277342</v>
     <v>7</v>
-    <v>15.75</v>
-    <v>3110795152</v>
+    <v>13.22</v>
+    <v>2614756998</v>
     <v>Bitdeer Technologies Group</v>
     <v>Bitdeer Technologies Group</v>
-    <v>15.95</v>
+    <v>13.435</v>
     <v>0</v>
-    <v>15.66</v>
-    <v>16.16</v>
-    <v>16.23</v>
-    <v>192499700</v>
+    <v>13.83</v>
+    <v>13.29</v>
+    <v>13.44</v>
+    <v>196746200</v>
     <v>BTDR</v>
     <v>Bitdeer Technologies Group (XNAS:BTDR)</v>
-    <v>3475948</v>
-    <v>7032926</v>
+    <v>2003500</v>
+    <v>4907259</v>
     <v>2021</v>
   </rv>
   <rv s="2">
@@ -55355,38 +55514,38 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>5.74</v>
-    <v>1.76</v>
-    <v>6.1253000000000002</v>
-    <v>0.17</v>
-    <v>5.8418999999999999E-2</v>
-    <v>0.01</v>
-    <v>3.2469999999999999E-3</v>
+    <v>1.69</v>
+    <v>5.3646000000000003</v>
+    <v>-0.09</v>
+    <v>-3.3457000000000001E-2</v>
+    <v>-1.9900000000000001E-2</v>
+    <v>-7.6539999999999993E-3</v>
     <v>USD</v>
-    <v>Bit Digital, Inc. is a holding company. The Company provides a platform for digital assets and artificial intelligence (AI) infrastructure headquartered in New York City. Its bitcoin mining operations are located in the United States, Canada, and Iceland. The Company’s business line, Bit Digital AI, offers infrastructure services for artificial intelligence applications. Its facilities and mining platform are operating with the primary intent of accumulating bitcoin, which the Company may sell for fiat currency from time to time depending on market conditions and management’s determination of its cash flow needs. The Company conducts its business through Bit Digital U.S.A. Inc., a Delaware corporation and its operating entity in the United States; Bit Digital Canada, Inc., its operating entity in Canada; Bit Digital Singapore Pte Ltd., a Singapore company, Bit Digital Hong Kong Limited and Bit Digital Strategies Limited, Hong Kong companies, and Bit Digital AI Inc.</v>
-    <v>24</v>
+    <v>Bit Digital, Inc. is a global platform for high performance computing (HPC) infrastructure and digital asset production company. The Company is a provider of HPC data centers and cloud-based HPC graphics processing units (GPU) services, which term cloud services, for customers such as artificial intelligence (AI) and machine learning (ML) developers. The Company designs, develops, and operates HPC data centers, through which it offers hosting and colocation services. The Company has four reportable segments: Digital asset mining, Cloud services, Colocation services, and ETH Staking. The Digital asset mining segment is engaged in bitcoin and mining activities. The Cloud services segment provides HPC services to support generative AI workstreams. The Colocation services segment provide customers with physical space, power and cooling within the data center facility. The ETH staking segment is engaged in both native staking and liquid staking.</v>
+    <v>54</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>31 HUDSON YARDS, FLOOR 11, NEW YORK, NY, 10001 US</v>
-    <v>3.09</v>
+    <v>2.69</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936096226564</v>
+    <v>45820.891214027346</v>
     <v>10</v>
-    <v>2.85</v>
-    <v>472808952</v>
+    <v>2.57</v>
+    <v>540230340</v>
     <v>BIT DIGITAL, INC</v>
     <v>BIT DIGITAL, INC</v>
-    <v>2.87</v>
-    <v>51.764699999999998</v>
-    <v>2.91</v>
-    <v>3.08</v>
-    <v>3.09</v>
-    <v>153509400</v>
+    <v>2.62</v>
+    <v>0</v>
+    <v>2.69</v>
+    <v>2.6</v>
+    <v>2.5800999999999998</v>
+    <v>207780900</v>
     <v>BTBT</v>
     <v>BIT DIGITAL, INC (XNAS:BTBT)</v>
-    <v>13601696</v>
-    <v>16738320</v>
+    <v>11622815</v>
+    <v>16893028</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -55409,38 +55568,38 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>9.3000000000000007</v>
-    <v>1.57</v>
-    <v>2.6999</v>
-    <v>0.09</v>
-    <v>1.8908000000000001E-2</v>
-    <v>7.0000000000000007E-2</v>
-    <v>1.4433E-2</v>
+    <v>2.06</v>
+    <v>3.1143999999999998</v>
+    <v>-0.15</v>
+    <v>-3.4014000000000003E-2</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
-    <v>TeraWulf Inc. owns and operates environmentally sustainable, data center infrastructure in the United States, specifically designed for bitcoin mining and high-performance computing. The Company owns and operates the Lake Mariner facility, which is located at a former coal power plant site in Western New York. It generates revenue primarily through bitcoin mining, leveraging predominantly zero-carbon energy sources, including nuclear and hydroelectric power. The Company is specializing in building and operating digital infrastructure to lead the energy transition through bitcoin mining and artificial intelligence (AI) and high-performance computing applications. The Company operates on a flexible infrastructure model, leveraging its core expertise in energy management to maximize operational efficiency while minimizing environmental impact.</v>
-    <v>10</v>
+    <v>TeraWulf Inc. develops, owns, and operates environmentally sustainable data center infrastructure in the United States, specifically designed for bitcoin mining and hosting HPC workloads. The Company owns and operates the Lake Mariner facility situated on the expansive site of a retired coal plant in Western New York. Lake Mariner is designed for scalable growth, with the capacity to expand up to 500 megawatts (MW) in the near term and 750 MW with certain transmission upgrades. The Company provides hash computation services to a mining pool operator, facilitating transaction validation of transactions on the global bitcoin network using its fleet of application-specific integrated circuit miners. Its purpose-built infrastructure provides HPC hosting and colocation services for GPU-based workloads, artificial intelligence, machine learning, and cloud computing applications. It also specializes in development and operation of power generation assets and related electrical infrastructure.</v>
+    <v>12</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>9 Federal Street, EASTON, MD, 21601 US</v>
-    <v>5.12</v>
+    <v>4.47</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936077233593</v>
+    <v>45820.889139594532</v>
     <v>13</v>
-    <v>4.6399999999999997</v>
-    <v>1871652344</v>
+    <v>4.24</v>
+    <v>1632166602</v>
     <v>TERAWULF INC.</v>
     <v>TERAWULF INC.</v>
-    <v>4.6950000000000003</v>
+    <v>4.3600000000000003</v>
     <v>0</v>
-    <v>4.76</v>
-    <v>4.8499999999999996</v>
-    <v>4.92</v>
-    <v>385907700</v>
+    <v>4.41</v>
+    <v>4.26</v>
+    <v>4.26</v>
+    <v>383137700</v>
     <v>WULF</v>
     <v>TERAWULF INC. (XNAS:WULF)</v>
-    <v>37238381</v>
-    <v>45843489</v>
+    <v>29921111</v>
+    <v>44140968</v>
     <v>2021</v>
   </rv>
   <rv s="2">
@@ -55462,13 +55621,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>24.72</v>
-    <v>8.0399999999999991</v>
-    <v>4.1779999999999999</v>
-    <v>0.24</v>
-    <v>2.3345999999999999E-2</v>
-    <v>7.0000000000000007E-2</v>
-    <v>6.6540000000000002E-3</v>
+    <v>20.64</v>
+    <v>6.452</v>
+    <v>4.2397999999999998</v>
+    <v>-0.26</v>
+    <v>-2.6078E-2</v>
+    <v>-3.9800000000000002E-2</v>
+    <v>-4.0990000000000002E-3</v>
     <v>USD</v>
     <v>CleanSpark, Inc. is a bitcoin mining company. The Company independently owns and operates data centers across the United States with locations in Georgia, Mississippi, Tennessee and Wyoming for a total contracted power capacity of approximately 853 megawatts (MW). The Company designs its infrastructure to responsibly secure and support the bitcoin network. Its operating mining units are capable of producing over 40 exahashes per second (EH/s) of computing power. The Company operates approximately 188,500 bitcoin mining machines, with a hashrate capacity of approximately 27.6 EH/s and a fleetwide efficiency of 21.94 joules per terahash (J/TH). The Company's subsidiaries include ATL Data Centers LLC, CleanBlok, Inc., CleanSpark DW, LLC, CleanSpark GLP, LLC, CSRE Properties Washington, LLC, CSRE Properties Dalton, LLC, CSRE Property Management Company, LLC, and CSRE Properties Norcross, LLC, among others.</v>
     <v>256</v>
@@ -55476,25 +55635,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>10624 S. Eastern Ave., Suite A - 638, HENDERSON, NV, 89052 US</v>
-    <v>10.61</v>
+    <v>10.06</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936206978906</v>
+    <v>45820.891392407029</v>
     <v>16</v>
-    <v>9.9700000000000006</v>
-    <v>2954095952</v>
+    <v>9.51</v>
+    <v>2727964298</v>
     <v>CLEANSPARK, INC.</v>
     <v>CLEANSPARK, INC.</v>
-    <v>10</v>
-    <v>77.364900000000006</v>
-    <v>10.28</v>
-    <v>10.52</v>
-    <v>10.59</v>
-    <v>280807600</v>
+    <v>9.65</v>
+    <v>0</v>
+    <v>9.9700000000000006</v>
+    <v>9.7100000000000009</v>
+    <v>9.6701999999999995</v>
+    <v>280943800</v>
     <v>CLSK</v>
     <v>CLEANSPARK, INC. (XNAS:CLSK)</v>
-    <v>18506542</v>
-    <v>24212298</v>
+    <v>19358600</v>
+    <v>28326923</v>
     <v>1987</v>
   </rv>
   <rv s="2">
@@ -55516,39 +55675,39 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>34.090000000000003</v>
-    <v>13.164999999999999</v>
-    <v>5.9347000000000003</v>
-    <v>0.22</v>
-    <v>1.3733E-2</v>
-    <v>0.16009999999999999</v>
-    <v>9.8580000000000004E-3</v>
+    <v>30.28</v>
+    <v>9.81</v>
+    <v>6.6241000000000003</v>
+    <v>-0.53</v>
+    <v>-3.2416E-2</v>
+    <v>-0.04</v>
+    <v>-2.5280000000000003E-3</v>
     <v>USD</v>
-    <v>MARA Holdings Inc, formerly Marathon Digital Holdings, Inc. is a digital asset compute that develops and deploys technologies. The Company’s digital asset compute portfolio spans multiple states and countries. It manages large grid-connected deployments that reduce energy waste and inefficiencies, as well as small, dispersed deployments that transform stranded or wasted energy resources into more productive and sustainable assets. Its technologies include 2PIC by MARA, MARAFW, MARA SLIPSTREAM, ANDURO, and ALYS. The Company’s 2PIC by MARA is a next generation of immersion cooling technology. MARATools provides a streamlined process for firmware installation, configuration, and management of ASICs. Anduro is a multi-sidechain platform on bitcoin. ALYS is a bitcoin sidechain where builders can use Ethereum smart contracts. The Company’s digital asset compute portfolio approximately 265,000 operational miners.</v>
-    <v>130</v>
+    <v>MARA Holdings, Inc. is engaged in digital asset compute that develops and deploys technologies. The Company secures the blockchain ledger and supports energy transformation by converting clean, stranded, or otherwise underutilized energy into economic value. It also offers advanced technology solutions to optimize data center operations, including liquid immersion cooling and firmware for bitcoin miners. It is primarily focused on computing for, acquiring, and holding digital assets as a long-term investment. Its core business is bitcoin mining, and it produces, or mines, bitcoin using energy-efficient fleets of specialized computers while providing dispatchable compute as an optionality to the electric grid operators to balance electric demands on the grid. It is also engaged in the sale of data center infrastructure, such as immersion-cooled systems, to third parties operating in the bitcoin ecosystem and the artificial intelligence (AI) and high-performance compute (HPC) sectors.</v>
+    <v>152</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>101 Ne Third Avenue,, Suite 1200, FORT LAUDERDALE, FL, 33301 US</v>
-    <v>16.37</v>
+    <v>16.48</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936400543753</v>
+    <v>45820.891551747656</v>
     <v>19</v>
-    <v>15.68</v>
-    <v>5511570175</v>
+    <v>15.61</v>
+    <v>5567497796</v>
     <v>MARA HOLDINGS, INC.</v>
     <v>MARA HOLDINGS, INC.</v>
-    <v>15.9</v>
-    <v>16.473800000000001</v>
-    <v>16.02</v>
-    <v>16.239999999999998</v>
-    <v>16.400099999999998</v>
-    <v>339382400</v>
+    <v>15.85</v>
+    <v>0</v>
+    <v>16.350000000000001</v>
+    <v>15.82</v>
+    <v>15.78</v>
+    <v>351927800</v>
     <v>MARA</v>
     <v>MARA HOLDINGS, INC. (XNAS:MARA)</v>
-    <v>23493332</v>
-    <v>35760324</v>
+    <v>42531923</v>
+    <v>49274203</v>
     <v>2010</v>
   </rv>
   <rv s="2">
@@ -55571,38 +55730,38 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>7.99</v>
-    <v>2.6549999999999998</v>
-    <v>2.4177</v>
-    <v>0.08</v>
-    <v>1.4034999999999999E-2</v>
-    <v>1.04E-2</v>
-    <v>1.799E-3</v>
+    <v>1.86</v>
+    <v>2.6120999999999999</v>
+    <v>-0.24</v>
+    <v>-5.8823999999999994E-2</v>
+    <v>0.02</v>
+    <v>5.2080000000000008E-3</v>
     <v>USD</v>
-    <v>Cipher Mining Inc. is a technology company focused on the development and operation of bitcoin mining data centers. The Company, through its subsidiaries, including Cipher Mining Technologies Inc., operates four bitcoin mining data centers in Texas. Its active portfolio and development pipeline will total 2.6 GW across 11 sites. Its operating data center is the Odessa data center (the Odessa Facility), which is its wholly owned 207 megawatts (MW) facility located in Odessa, Texas. It also jointly operates the Alborz data center (the Alborz Facility), located near Happy, Texas, and the Bear data center (the Bear Facility) and the Chief data center (the Chief Facility), each of which is located near Andrews, Texas (the Data Center LLCs). It also owns the Barber Lake site in West Texas. Barber Lake site features 300 MW of front-of-the-meter capacity. It also owns the 100 MW Stingray site in West Texas.</v>
-    <v>35</v>
+    <v>Cipher Mining Inc. is an industrial-scale data center construction and operations company. The Company is focused on the development and operation of industrial-scale data centers for bitcoin mining and high-performance computing (HPC) hosting. It operates approximately 327 MW of facilities across four bitcoin mining data centers in Texas, including one wholly owned data center and three partially owned data centers. The Company also has a pipeline of 2.8 GW across seven additional sites in Texas. It operates an aggregate hash rate capacity of 15.7 exahash per second (EH/s). Its operational data center is its Odessa data center, which is its wholly owned 207 MW facility located in Odessa, Texas. Its Alborz data center is located near Happy, Texas. Its Bear data center is located near Andrews, Texas. Its Black Pearl data center is in Winkler County, Texas. Its Barber Lake site is located near Colorado City, Texas. Stingray site is in West Texas. Its Reveille site is in Cotulla, Texas.</v>
+    <v>43</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1 Vanderbilt Avenue, Floor 54, NEW YORK, NY, 10017 US</v>
-    <v>5.9250999999999996</v>
+    <v>4.04</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.930130647655</v>
+    <v>45820.89020489531</v>
     <v>22</v>
-    <v>5.53</v>
-    <v>2028835488</v>
+    <v>3.83</v>
+    <v>1287444096</v>
     <v>CIPHER MINING INC.</v>
     <v>CIPHER MINING INC.</v>
-    <v>5.53</v>
+    <v>3.91</v>
     <v>0</v>
-    <v>5.7</v>
-    <v>5.78</v>
-    <v>5.7904</v>
-    <v>351009600</v>
+    <v>4.08</v>
+    <v>3.84</v>
+    <v>3.86</v>
+    <v>335271900</v>
     <v>CIFR</v>
     <v>CIPHER MINING INC. (XNAS:CIFR)</v>
-    <v>6907797</v>
-    <v>12470576</v>
+    <v>19372223</v>
+    <v>23191746</v>
     <v>2020</v>
   </rv>
   <rv s="2">
@@ -55624,39 +55783,39 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>18.36</v>
-    <v>6.3550000000000004</v>
-    <v>4.3300999999999998</v>
-    <v>0.02</v>
-    <v>1.7949999999999999E-3</v>
-    <v>0.06</v>
-    <v>5.3759999999999997E-3</v>
+    <v>15.87</v>
+    <v>6.19</v>
+    <v>4.5506000000000002</v>
+    <v>-0.34</v>
+    <v>-3.2226999999999999E-2</v>
+    <v>-0.02</v>
+    <v>-1.9589999999999998E-3</v>
     <v>USD</v>
-    <v>Riot Platforms, Inc. is a Bitcoin mining and digital infrastructure company. The Company has Bitcoin mining operations in central Texas and Kentucky, and electrical switchgear engineering and fabrication operations in Denver, Colorado. It operates a Bitcoin-driven infrastructure platform. Its segments include Bitcoin Mining and Engineering. The Bitcoin Mining segment is engaged in Bitcoin mining activities. The Engineering segment designs and manufacturers power distribution equipment and custom engineered electrical products. The Engineering segment also provides electricity distribution product design, manufacturing, and installation services primarily focused on large-scale commercial and governmental customers and serves a broad scope of clients across a wide range of markets including data center, power generation, utility, water, industrial, and alternative energy. The Company’s total potential power capacity is two gigawatts.</v>
-    <v>534</v>
+    <v>Riot Platforms, Inc. is a Bitcoin mining and digital infrastructure company. The Company has Bitcoin mining operations in central Texas and Kentucky, and electrical engineering and fabrication operations in Denver, Colorado, and Houston, Texas. It operates a Bitcoin-driven infrastructure platform. Its segments include Bitcoin Mining and Engineering. The Bitcoin Mining segment is engaged in Bitcoin mining activities. The Engineering segment designs and manufacturers power distribution equipment and custom engineered electrical products. This segment also provides electricity distribution product design, manufacturing, and installation services primarily focused on large-scale commercial and governmental customers and serves clients across a range of markets including data center, power generation, utility, water, industrial, and alternative energy. It is also focused on developing a portion of its power capacity for artificial intelligence (AI)/ high-performance computing (HPC) uses.</v>
+    <v>783</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>3855 AMBROSIA STREET, SUITE 301, CASTLE ROCK, CO, 80109 US</v>
-    <v>11.32</v>
+    <v>10.635</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936113865624</v>
+    <v>45820.891390543751</v>
     <v>25</v>
-    <v>10.88</v>
-    <v>3838226436</v>
+    <v>10.125</v>
+    <v>3647662377</v>
     <v>Riot Platforms, Inc.</v>
     <v>Riot Platforms, Inc.</v>
-    <v>10.97</v>
-    <v>31.194099999999999</v>
-    <v>11.14</v>
-    <v>11.16</v>
-    <v>11.22</v>
-    <v>343927100</v>
+    <v>10.23</v>
+    <v>0</v>
+    <v>10.55</v>
+    <v>10.210000000000001</v>
+    <v>10.19</v>
+    <v>357263700</v>
     <v>RIOT</v>
     <v>Riot Platforms, Inc. (XNAS:RIOT)</v>
-    <v>16014198</v>
-    <v>33042601</v>
+    <v>26317048</v>
+    <v>35198905</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -55675,37 +55834,37 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>18.628799999999998</v>
-    <v>2.61</v>
-    <v>4</v>
-    <v>-0.17</v>
-    <v>-1.3866E-2</v>
-    <v>0.06</v>
-    <v>4.9630000000000004E-3</v>
+    <v>6.2</v>
+    <v>2.6819999999999999</v>
+    <v>-0.11</v>
+    <v>-8.9800000000000001E-3</v>
+    <v>-1.6E-2</v>
+    <v>-1.3179999999999999E-3</v>
     <v>USD</v>
     <v>Core Scientific, Inc. provides digital infrastructure for bitcoin mining and high-performance computing. The Company operates dedicated, purpose-built facilities for digital asset mining. It provides digital infrastructure, software solutions and services to its third-party customers. It employs its own fleet of computers (miners) to earn bitcoin for its own account and provides hosting services for bitcoin mining and high-performance computing customers at its eight operational data centers in Georgia (two), Kentucky (one), North Carolina (one), North Dakota (one) and Texas (three). Its segments include Digital Asset Self-Mining, Digital Asset Hosted Mining and HPC Hosting. Digital Asset Self-Mining segment consists of digital asset mining for its own account. Digital Asset Hosted Mining segment consists of its digital infrastructure and third-party hosting services for digital asset mining. HPC Hosting segment consists of its hosting services for high-performance compute operations.</v>
-    <v>286</v>
+    <v>325</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
-    <v>106 East 6Th Street, Suite 900-145, AUSTIN, TX, 78701 US</v>
-    <v>12.25</v>
+    <v>838 Walker Road, Suite 21-2105, DOVER, DE, 19904 US</v>
+    <v>12.545</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936206885941</v>
-    <v>11.71</v>
-    <v>3376168770</v>
+    <v>45820.884428853904</v>
+    <v>12.02</v>
+    <v>3615556652</v>
     <v>CORE SCIENTIFIC, INC.</v>
     <v>CORE SCIENTIFIC, INC.</v>
-    <v>11.96</v>
+    <v>12.08</v>
     <v>0</v>
-    <v>12.26</v>
-    <v>12.09</v>
-    <v>12.15</v>
-    <v>279253000</v>
+    <v>12.25</v>
+    <v>12.14</v>
+    <v>12.124000000000001</v>
+    <v>297821800</v>
     <v>CORZ</v>
     <v>CORE SCIENTIFIC, INC. (XNAS:CORZ)</v>
-    <v>7321108</v>
-    <v>11642570</v>
+    <v>4277701</v>
+    <v>12302479</v>
     <v>2020</v>
   </rv>
   <rv s="2">
@@ -55728,38 +55887,38 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>5.54</v>
-    <v>2.1800000000000002</v>
-    <v>4.5587</v>
-    <v>0.03</v>
-    <v>1.1029000000000001E-2</v>
-    <v>1.06E-2</v>
-    <v>3.8549999999999999E-3</v>
+    <v>1.26</v>
+    <v>5.2961999999999998</v>
+    <v>-0.05</v>
+    <v>-2.5000000000000001E-2</v>
+    <v>0.04</v>
+    <v>2.0513E-2</v>
     <v>USD</v>
-    <v>HIVE Digital Technologies Ltd. is a Canada-based cryptocurrency mining company that focus on sustainable green energy. The Company is engaged in building a bridge between the digital currency and blockchain sector and traditional capital markets. It owns and operates predominantly green energy powered data center facilities in Canada, Sweden, and Iceland. It also owns hard assets such as data centers and advanced multi-use servers. It operates a fleet of approximately 38,000 commercial-grade NVIDIA graphic processing units (GPUs). Its GPU fleet includes 4,000+ NVIDIA A40s w/ 48 GB RAM, 400+ NVIDIA RTX A6000s w/ 48 GB RAM, 12,000+ NVIDIA RTX A5000s w/ 24 GB RAM and 20,000+ NVIDIA RTX A4000s w/ 16 GB RAM. The Company, through its subsidiary HIVE Performance Computing Ltd., is building HIVE Cloud, an enterprise-grade GPU Cloud service for demanding applications including AI training and inference. It operates over 100 MW of data centers in Canada and 46 MW in Iceland and Sweden.</v>
+    <v>HIVE Digital Technologies Ltd. is a technology company advancing sustainable blockchain and artificial intelligence (AI) infrastructure powered by green energy. The Company is engaged in digital asset mining and AI computing. Its operations are focused on the mining of digital currencies to upgrade, expand and scale up its data center operations. It holds Bitcoin and monetizes other cryptocurrencies that it derives from its mining operations. It is engaged in building a bridge between the Bitcoin blockchain sector and traditional capital markets. Its cryptocurrency assets provide shareholders with exposure to the operating margins of digital currency mining as well as a portfolio of Bitcoin. It develops and expands its high-performance computing business, which implements the Company’s fleet of graphic processing units (GPUs) in enterprise-grade CPU servers, operating in tier three data centers. It operates green energy-powered data center facilities in Canada, Sweden, and Paraguay.</v>
     <v>18</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
-    <v>855 - 789 West Pender Street, VANCOUVER, BC, V6C 1H2 CA</v>
-    <v>2.7890000000000001</v>
+    <v>370-1095 West Pender Street, VANCOUVER, BC, V6E 2M6 CA</v>
+    <v>2.0099999999999998</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936188310159</v>
+    <v>45820.89114716406</v>
     <v>30</v>
-    <v>2.65</v>
-    <v>580442400</v>
+    <v>1.92</v>
+    <v>513033200</v>
     <v>HIVE DIGITAL TECHNOLOGIES LTD.</v>
     <v>HIVE DIGITAL TECHNOLOGIES LTD.</v>
-    <v>2.7149999999999999</v>
+    <v>1.98</v>
     <v>0</v>
-    <v>2.72</v>
-    <v>2.75</v>
-    <v>2.7606000000000002</v>
-    <v>148072000</v>
+    <v>2</v>
+    <v>1.95</v>
+    <v>1.99</v>
+    <v>187238400</v>
     <v>HIVE</v>
     <v>HIVE DIGITAL TECHNOLOGIES LTD. (XNAS:HIVE)</v>
-    <v>8202537</v>
-    <v>11002238</v>
+    <v>17314361</v>
+    <v>16003086</v>
     <v>1987</v>
   </rv>
   <rv s="2">
@@ -55781,39 +55940,39 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>3.91</v>
-    <v>1.28</v>
-    <v>3.2444999999999999</v>
-    <v>0.05</v>
-    <v>3.8168000000000001E-2</v>
-    <v>0.01</v>
-    <v>7.3529999999999993E-3</v>
+    <v>3.28</v>
+    <v>0.67300000000000004</v>
+    <v>4.1547999999999998</v>
+    <v>-2.58E-2</v>
+    <v>-2.8801E-2</v>
+    <v>2.5000000000000001E-3</v>
+    <v>2.8739999999999998E-3</v>
     <v>USD</v>
-    <v>Bitfarms Ltd. is a global vertically integrated Bitcoin data center company that contributes its computational power to one or more mining pools. It develops, owns, and operates vertically integrated mining facilities with in-house management and Company-owned electrical engineering, installation service, and multiple onsite technical repair centers. Its proprietary data analytics system delivers operational performance and uptime. The Company operates through the cryptocurrency mining segment. The activities of the Company mainly consist of selling its computational power used for hashing calculations for the purpose of cryptocurrency mining in multiple jurisdictions. Volta, a wholly owned subsidiary of the Company, assists the Company in building and maintaining its data centers. It has about 12 operating Bitcoin data centers and two under development, as well as hosting agreements with two data centers, in four countries: Canada, the United States, Paraguay, and Argentina.</v>
+    <v>Bitfarms Ltd. is a Canada-based global Bitcoin and vertically integrated data center company that sells its computational power to one or more mining pools from which it receives payment in Bitcoin. It develops, owns, and operates vertically integrated mining facilities with in-house management and Company-owned electrical engineering, installation service, and multiple onsite technical repair centers. Its proprietary data analytics system delivers operational performance and uptime. The Company operates through the cryptocurrency mining segment. The activities of the Company mainly consist of selling its computational power used for hashing calculations for the purpose of cryptocurrency mining in multiple jurisdictions. Volta, a wholly owned subsidiary of the Company, assists the Company in building and maintaining its data centers. The Company operates Bitcoin data centers in four countries: the United States, Canada, Paraguay, and Argentina.</v>
     <v>170</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>110 Yonge Street, Suite 1601, TORONTO, ON, M5C 1T4 CA</v>
-    <v>1.4</v>
+    <v>0.88890000000000002</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.935812453128</v>
+    <v>45820.88953743047</v>
     <v>33</v>
-    <v>1.28</v>
-    <v>851518400</v>
+    <v>0.86009999999999998</v>
+    <v>683832800</v>
     <v>BITFARMS LTD.</v>
     <v>BITFARMS LTD.</v>
-    <v>1.29</v>
+    <v>0.87990000000000002</v>
     <v>0</v>
-    <v>1.31</v>
-    <v>1.36</v>
-    <v>1.37</v>
-    <v>452935300</v>
+    <v>0.89580000000000004</v>
+    <v>0.87</v>
+    <v>0.87250000000000005</v>
+    <v>555961600</v>
     <v>BITF</v>
     <v>BITFARMS LTD. (XNAS:BITF)</v>
-    <v>51891803</v>
-    <v>43536523</v>
+    <v>8264622</v>
+    <v>20658834</v>
     <v>2018</v>
   </rv>
   <rv s="2">
@@ -55836,35 +55995,35 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>7.75</v>
-    <v>3</v>
-    <v>4.5587</v>
-    <v>0.01</v>
-    <v>2.5509999999999999E-3</v>
+    <v>1.8</v>
+    <v>5.2961999999999998</v>
+    <v>-0.08</v>
+    <v>-2.9197000000000001E-2</v>
     <v>CAD</v>
-    <v>HIVE Digital Technologies Ltd. is a Canada-based cryptocurrency mining company that focus on sustainable green energy. The Company is engaged in building a bridge between the digital currency and blockchain sector and traditional capital markets. It owns and operates predominantly green energy powered data center facilities in Canada, Sweden, and Iceland. It also owns hard assets such as data centers and advanced multi-use servers. It operates a fleet of approximately 38,000 commercial-grade NVIDIA graphic processing units (GPUs). Its GPU fleet includes 4,000+ NVIDIA A40s w/ 48 GB RAM, 400+ NVIDIA RTX A6000s w/ 48 GB RAM, 12,000+ NVIDIA RTX A5000s w/ 24 GB RAM and 20,000+ NVIDIA RTX A4000s w/ 16 GB RAM. The Company, through its subsidiary HIVE Performance Computing Ltd., is building HIVE Cloud, an enterprise-grade GPU Cloud service for demanding applications including AI training and inference. It operates over 100 MW of data centers in Canada and 46 MW in Iceland and Sweden.</v>
+    <v>HIVE Digital Technologies Ltd. is a technology company advancing sustainable blockchain and artificial intelligence (AI) infrastructure powered by green energy. The Company is engaged in digital asset mining and AI computing. Its operations are focused on the mining of digital currencies to upgrade, expand and scale up its data center operations. It holds Bitcoin and monetizes other cryptocurrencies that it derives from its mining operations. It is engaged in building a bridge between the Bitcoin blockchain sector and traditional capital markets. Its cryptocurrency assets provide shareholders with exposure to the operating margins of digital currency mining as well as a portfolio of Bitcoin. It develops and expands its high-performance computing business, which implements the Company’s fleet of graphic processing units (GPUs) in enterprise-grade CPU servers, operating in tier three data centers. It operates green energy-powered data center facilities in Canada, Sweden, and Paraguay.</v>
     <v>18</v>
     <v>TSX Venture Exchange</v>
     <v>XTSX</v>
     <v>XTSX</v>
-    <v>855 - 789 West Pender Street, VANCOUVER, BC, V6C 1H2 CA</v>
-    <v>3.97</v>
+    <v>370-1095 West Pender Street, VANCOUVER, BC, V6E 2M6 CA</v>
+    <v>2.74</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.875</v>
+    <v>45820.833333333336</v>
     <v>36</v>
-    <v>3.81</v>
-    <v>581922960</v>
+    <v>2.62</v>
+    <v>498054144</v>
     <v>HIVE DIGITAL TECHNOLOGIES LTD.</v>
     <v>HIVE DIGITAL TECHNOLOGIES LTD.</v>
-    <v>3.9</v>
+    <v>2.7</v>
     <v>0</v>
-    <v>3.92</v>
-    <v>3.93</v>
-    <v>148072000</v>
+    <v>2.74</v>
+    <v>2.66</v>
+    <v>187238400</v>
     <v>HIVE</v>
     <v>HIVE DIGITAL TECHNOLOGIES LTD. (XTSX:HIVE)</v>
-    <v>582891</v>
-    <v>983900</v>
+    <v>406775</v>
+    <v>666470</v>
     <v>1987</v>
   </rv>
   <rv s="2">
@@ -55887,38 +56046,38 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>31.95</v>
-    <v>6.77</v>
-    <v>3.7866</v>
-    <v>0.23</v>
-    <v>1.1448E-2</v>
-    <v>0.32840000000000003</v>
-    <v>1.6161000000000002E-2</v>
+    <v>8.7308000000000003</v>
+    <v>3.9586000000000001</v>
+    <v>-0.16</v>
+    <v>-8.6390000000000008E-3</v>
+    <v>-9.9900000000000003E-2</v>
+    <v>-5.4410000000000005E-3</v>
     <v>USD</v>
-    <v>Hut 8 Corp. is a data mining company. The Company is a vertically integrated operator of large-scale energy infrastructure and bitcoin miner. The Company acquires, designs, builds, manages, and operates data centers that power compute-intensive workloads, such as bitcoin mining, high performance computing, and artificial intelligence (AI). The Company operates through four business segments: Digital Assets Mining, Managed Services, High Performance Computing-Colocation and Cloud, and Other. Its infrastructure portfolio includes about eighteen sites: nine Bitcoin mining, hosting, and Managed Services sites in Alberta, New York, Nebraska, and Texas, five high performance computing data centers in British Columbia and Ontario, and four power generation assets in Ontario. Its Managed Services business provides institutional partners such as digital asset mining site owners, governments, and data center developers an end-to-end partnership model for energy infrastructure development.</v>
-    <v>219</v>
+    <v>Hut 8 Corp. is an energy infrastructure platform. The Company's segments include Power, Digital Infrastructure, Compute, and Other. The Company's Power segment acquires, develops, and manages critical energy assets such as interconnects, powered land, and other electrical infrastructure to address the load demands of energy-intensive applications such as Bitcoin mining and high-performance computing. Its Power segment consists of power generation and managed services. Its Digital Infrastructure segment consists of CPU Colocation and ASIC Colocation services. The Company's Compute segment consists of Bitcoin Mining, GPU-as-a-Service, and Data Center Cloud operations. The Company, through its subsidiary, American Bitcoin Corp., is focused exclusively on industrial-scale Bitcoin mining and strategic Bitcoin reserve development. The Company's platform spans approximately 1,020 megawatts of energy capacity under management across 15 sites in the United States and Canada.</v>
+    <v>222</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1101 Brickell Avenue, Suite 1500, MIAMI, FL, 33131 US</v>
-    <v>20.515000000000001</v>
+    <v>18.940000000000001</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.936439015626</v>
+    <v>45820.889687753908</v>
     <v>39</v>
-    <v>19.420000000000002</v>
-    <v>2107698096</v>
+    <v>17.79</v>
+    <v>1931409000</v>
     <v>HUT 8 CORP.</v>
     <v>HUT 8 CORP.</v>
-    <v>19.809999999999999</v>
-    <v>9.5855999999999995</v>
-    <v>20.09</v>
-    <v>20.32</v>
-    <v>20.648399999999999</v>
-    <v>103725300</v>
+    <v>17.829999999999998</v>
+    <v>0</v>
+    <v>18.52</v>
+    <v>18.36</v>
+    <v>18.260100000000001</v>
+    <v>104169300</v>
     <v>HUT</v>
     <v>HUT 8 CORP. (XNAS:HUT)</v>
-    <v>2033217</v>
-    <v>5392939</v>
+    <v>4019481</v>
+    <v>7719018</v>
     <v>2023</v>
   </rv>
   <rv s="2">
@@ -55941,34 +56100,34 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>0.14000000000000001</v>
-    <v>5.5E-2</v>
-    <v>3.2444000000000002</v>
-    <v>0</v>
-    <v>0</v>
+    <v>2.5000000000000001E-2</v>
+    <v>5.4848999999999997</v>
+    <v>1.4999999999999999E-2</v>
+    <v>0.272727</v>
     <v>CAD</v>
-    <v>Cathedra Bitcoin Inc. is a Canada-based bitcoin company. The Company develops and operates a high-density compute infrastructure across North America. It hosts bitcoin mining clients across its portfolio of three data centers (30 megawatts total) in Tennessee and Kentucky. The Company operates a fleet of proprietary bitcoin mining machines at its own and third-party data centers, producing approximately 400 Peta hashes per second (PH/s) of hash rate. It is focused on expanding its portfolio of data center infrastructure for high-density compute applications, including bitcoin mining and artificial intelligence. The Company is focused on managing and expanding its portfolio of hash rates through a diversified approach to site selection and operations, utilizing multiple energy sources across various jurisdictions.</v>
+    <v>Cathedra Bitcoin Inc. is a Canada-based bitcoin company. The Company develops and operates a high-density compute infrastructure across North America. It hosts bitcoin mining clients across its portfolio of three data centers (30 megawatts total) in Tennessee and Kentucky. The Company operates a fleet of proprietary bitcoin mining machines at its own and third-party data centers, producing approximately 400 Peta hashes per second (PH/s) of hash rate. It is focused on expanding its portfolio of data center infrastructure for high-density compute applications, including bitcoin mining and artificial intelligence.</v>
     <v>TSX Venture Exchange</v>
     <v>XTSX</v>
     <v>XTSX</v>
     <v>320-638 Broughton St, Vancouver, BC, V6G 3K3 CA</v>
-    <v>6.5000000000000002E-2</v>
+    <v>7.0000000000000007E-2</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>45700.839560185188</v>
+    <v>45820.829976851855</v>
     <v>42</v>
-    <v>0.06</v>
-    <v>15944032</v>
+    <v>0.05</v>
+    <v>17177314</v>
     <v>Cathedra Bitcoin Inc.</v>
     <v>Cathedra Bitcoin Inc.</v>
-    <v>6.5000000000000002E-2</v>
-    <v>3.9561999999999999</v>
-    <v>6.5000000000000002E-2</v>
-    <v>6.5000000000000002E-2</v>
-    <v>245292800</v>
+    <v>5.5E-2</v>
+    <v>0</v>
+    <v>5.5E-2</v>
+    <v>7.0000000000000007E-2</v>
+    <v>245390200</v>
     <v>CBIT</v>
     <v>Cathedra Bitcoin Inc. (XTSX:CBIT)</v>
-    <v>246943</v>
-    <v>145880</v>
+    <v>619502</v>
+    <v>362050</v>
     <v>2018</v>
   </rv>
   <rv s="2">
@@ -57107,7 +57266,7 @@
       </c>
       <c r="E2" s="21" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">_FV(D2,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -57116,14 +57275,14 @@
       </c>
       <c r="B3" s="57" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A2,"Price")</f>
-        <v>13.01</v>
+        <v>10.17</v>
       </c>
       <c r="D3" s="45" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="E3" s="21" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">_FV(D3,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -57132,7 +57291,7 @@
       </c>
       <c r="B4" s="24" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">_FV(A2,"Market cap",TRUE)</f>
-        <v>2789418157</v>
+        <v>2282747013</v>
       </c>
       <c r="C4" s="56"/>
       <c r="D4" s="1"/>
@@ -57144,7 +57303,7 @@
       </c>
       <c r="B5" s="59" cm="1">
         <f t="array" aca="1" ref="B5" ca="1">_FV(A2,"Shares outstanding",TRUE)</f>
-        <v>214405700</v>
+        <v>224458900</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -57188,7 +57347,7 @@
       </c>
       <c r="B9" s="22">
         <f ca="1">B6/B5</f>
-        <v>3.1586846804912367</v>
+        <v>3.0172116142420728</v>
       </c>
       <c r="D9" s="1"/>
       <c r="F9" s="23"/>
@@ -57199,7 +57358,7 @@
       </c>
       <c r="B10" s="26">
         <f ca="1">B3/B9</f>
-        <v>4.1188030196090013</v>
+        <v>3.3706618229874197</v>
       </c>
       <c r="D10" s="1"/>
       <c r="F10" s="23"/>
@@ -57363,7 +57522,7 @@
       </c>
       <c r="B29" s="14" cm="1">
         <f t="array" aca="1" ref="B29" ca="1">_FV(A28,"Price")</f>
-        <v>16.16</v>
+        <v>13.29</v>
       </c>
       <c r="D29" s="1"/>
     </row>
@@ -57373,7 +57532,7 @@
       </c>
       <c r="B30" s="28" cm="1">
         <f t="array" aca="1" ref="B30" ca="1">_FV(A28,"Market cap",TRUE)</f>
-        <v>3110795152</v>
+        <v>2614756998</v>
       </c>
       <c r="D30" s="1"/>
     </row>
@@ -57383,7 +57542,7 @@
       </c>
       <c r="B31" s="1" cm="1">
         <f t="array" aca="1" ref="B31" ca="1">_FV(A28,"Shares outstanding",TRUE)</f>
-        <v>192499700</v>
+        <v>196746200</v>
       </c>
       <c r="D31" s="1"/>
     </row>
@@ -57423,7 +57582,7 @@
       </c>
       <c r="B35" s="25">
         <f ca="1">B32/B31</f>
-        <v>2.0330057657232712</v>
+        <v>1.9891260923972103</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -57435,7 +57594,7 @@
       </c>
       <c r="B36" s="26">
         <f ca="1">B29/B35</f>
-        <v>7.9488215294120659</v>
+        <v>6.6813260611263994</v>
       </c>
       <c r="D36" s="1"/>
       <c r="F36" s="23"/>
@@ -57594,7 +57753,7 @@
       </c>
       <c r="B56" s="14" cm="1">
         <f t="array" aca="1" ref="B56" ca="1">_FV(A55,"Price")</f>
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
@@ -57603,7 +57762,7 @@
       </c>
       <c r="B57" s="28" cm="1">
         <f t="array" aca="1" ref="B57" ca="1">_FV(A55,"Market cap",TRUE)</f>
-        <v>472808952</v>
+        <v>540230340</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
@@ -57612,7 +57771,7 @@
       </c>
       <c r="B58" s="1" cm="1">
         <f t="array" aca="1" ref="B58" ca="1">_FV(A55,"Shares outstanding",TRUE)</f>
-        <v>153509400</v>
+        <v>207780900</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
@@ -57645,7 +57804,7 @@
       </c>
       <c r="B62" s="25">
         <f ca="1">B59/B58</f>
-        <v>1.727513357488206</v>
+        <v>1.2762941107676404</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -57654,7 +57813,7 @@
       </c>
       <c r="B63" s="26">
         <f ca="1">B56/B62</f>
-        <v>1.7829095136365842</v>
+        <v>2.0371480037906018</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -57671,7 +57830,7 @@
       </c>
       <c r="B65" s="42">
         <f ca="1">(B64*E2)</f>
-        <v>93551416.280000001</v>
+        <v>101616796.32000001</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -57688,7 +57847,7 @@
       </c>
       <c r="B67" s="42">
         <f ca="1">(B66*E3)</f>
-        <v>44027698.710000001</v>
+        <v>42524632.149999999</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -57779,7 +57938,7 @@
       </c>
       <c r="B79" s="14" cm="1">
         <f t="array" aca="1" ref="B79" ca="1">_FV(A78,"Price")</f>
-        <v>4.8499999999999996</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -57788,7 +57947,7 @@
       </c>
       <c r="B80" s="28" cm="1">
         <f t="array" aca="1" ref="B80" ca="1">_FV(A78,"Market cap",TRUE)</f>
-        <v>1871652344</v>
+        <v>1632166602</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -57797,7 +57956,7 @@
       </c>
       <c r="B81" s="1" cm="1">
         <f t="array" aca="1" ref="B81" ca="1">_FV(A78,"Shares outstanding",TRUE)</f>
-        <v>385907700</v>
+        <v>383137700</v>
       </c>
       <c r="E81" s="27"/>
       <c r="F81" s="23"/>
@@ -57838,7 +57997,7 @@
       </c>
       <c r="B85" s="25">
         <f ca="1">B82/B81</f>
-        <v>0.70572056478790135</v>
+        <v>0.71082276685379697</v>
       </c>
       <c r="F85" s="23"/>
     </row>
@@ -57848,7 +58007,7 @@
       </c>
       <c r="B86" s="26">
         <f ca="1">B79/B85</f>
-        <v>6.8724084885603816</v>
+        <v>5.9930550886198652</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
@@ -57976,7 +58135,7 @@
       </c>
       <c r="B103" s="14" cm="1">
         <f t="array" aca="1" ref="B103" ca="1">_FV(A102,"Price")</f>
-        <v>10.52</v>
+        <v>9.7100000000000009</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -57985,7 +58144,7 @@
       </c>
       <c r="B104" s="28" cm="1">
         <f t="array" aca="1" ref="B104" ca="1">_FV(A102,"Market cap",TRUE)</f>
-        <v>2954095952</v>
+        <v>2727964298</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -57994,7 +58153,7 @@
       </c>
       <c r="B105" s="1" cm="1">
         <f t="array" aca="1" ref="B105" ca="1">_FV(A102,"Shares outstanding",TRUE)</f>
-        <v>280807600</v>
+        <v>280943800</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
@@ -58027,7 +58186,7 @@
       </c>
       <c r="B109" s="25">
         <f ca="1">B106/B105</f>
-        <v>5.2096773734044239</v>
+        <v>5.2071517506348242</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -58036,7 +58195,7 @@
       </c>
       <c r="B110" s="26">
         <f ca="1">B103/B109</f>
-        <v>2.0193189032597201</v>
+        <v>1.8647430428383842</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -58053,7 +58212,7 @@
       </c>
       <c r="B112" s="42">
         <f ca="1">B111*E2</f>
-        <v>561602069.07000005</v>
+        <v>610019659.08000004</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -58180,7 +58339,7 @@
       </c>
       <c r="B128" s="14" cm="1">
         <f t="array" aca="1" ref="B128" ca="1">_FV(A127,"Price")</f>
-        <v>16.239999999999998</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -58189,7 +58348,7 @@
       </c>
       <c r="B129" s="28" cm="1">
         <f t="array" aca="1" ref="B129" ca="1">_FV(A127,"Market cap",TRUE)</f>
-        <v>5511570175</v>
+        <v>5567497796</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
@@ -58198,7 +58357,7 @@
       </c>
       <c r="B130" s="1" cm="1">
         <f t="array" aca="1" ref="B130" ca="1">_FV(A127,"Shares outstanding",TRUE)</f>
-        <v>339382400</v>
+        <v>351927800</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
@@ -58215,7 +58374,7 @@
       </c>
       <c r="B132" s="25">
         <f ca="1">B131/B130</f>
-        <v>7.2982364436105112</v>
+        <v>7.0380714453362305</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
@@ -58224,7 +58383,7 @@
       </c>
       <c r="B133" s="26">
         <f ca="1">B128/B132</f>
-        <v>2.2251951037045199</v>
+        <v>2.2477748518002194</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -58265,7 +58424,7 @@
       </c>
       <c r="B138" s="18">
         <f ca="1">B137*E2</f>
-        <v>1656721210.9000001</v>
+        <v>1799552679.5999999</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
@@ -58331,7 +58490,7 @@
       </c>
       <c r="B148" s="14" cm="1">
         <f t="array" aca="1" ref="B148" ca="1">_FV(A147,"Price")</f>
-        <v>5.78</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -58340,7 +58499,7 @@
       </c>
       <c r="B149" s="28" cm="1">
         <f t="array" aca="1" ref="B149" ca="1">_FV(A147,"Market cap",TRUE)</f>
-        <v>2028835488</v>
+        <v>1287444096</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -58349,7 +58508,7 @@
       </c>
       <c r="B150" s="1" cm="1">
         <f t="array" aca="1" ref="B150" ca="1">_FV(A147,"Shares outstanding",TRUE)</f>
-        <v>351009600</v>
+        <v>335271900</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -58366,7 +58525,7 @@
       </c>
       <c r="B152" s="25">
         <f ca="1">B151/B150</f>
-        <v>1.7119873644481518</v>
+        <v>1.7923482403386624</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -58375,7 +58534,7 @@
       </c>
       <c r="B153" s="26">
         <f ca="1">B148/B152</f>
-        <v>3.376193142560457</v>
+        <v>2.1424408011662042</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -58395,7 +58554,7 @@
       </c>
       <c r="B155" s="18">
         <f ca="1">(B154*E2)</f>
-        <v>198943545.29000002</v>
+        <v>216095132.75999999</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -58493,7 +58652,7 @@
       </c>
       <c r="B169" s="14" cm="1">
         <f t="array" aca="1" ref="B169" ca="1">_FV(A168,"Price")</f>
-        <v>11.16</v>
+        <v>10.210000000000001</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
@@ -58502,7 +58661,7 @@
       </c>
       <c r="B170" s="28" cm="1">
         <f t="array" aca="1" ref="B170" ca="1">_FV(A168,"Market cap",TRUE)</f>
-        <v>3838226436</v>
+        <v>3647662377</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
@@ -58511,7 +58670,7 @@
       </c>
       <c r="B171" s="1" cm="1">
         <f t="array" aca="1" ref="B171" ca="1">_FV(A168,"Shares outstanding",TRUE)</f>
-        <v>343927100</v>
+        <v>357263700</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
@@ -58529,7 +58688,7 @@
       </c>
       <c r="B173" s="25">
         <f ca="1">B172/B171</f>
-        <v>7.1974671376579513</v>
+        <v>6.9287867757065715</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
@@ -58538,7 +58697,7 @@
       </c>
       <c r="B174" s="26">
         <f ca="1">B169/B173</f>
-        <v>1.5505454608621461</v>
+        <v>1.4735624475843137</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
@@ -58587,7 +58746,7 @@
       </c>
       <c r="B180" s="18">
         <f ca="1">B179*E2</f>
-        <v>830807033.70000005</v>
+        <v>902433682.79999995</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
@@ -58668,7 +58827,7 @@
       </c>
       <c r="I1" s="21" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_FV(H1,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="K1" s="81" t="s">
         <v>111</v>
@@ -58697,7 +58856,7 @@
       </c>
       <c r="I2" s="21" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">_FV(H2,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>124</v>
@@ -58717,15 +58876,15 @@
       </c>
       <c r="B3" s="15" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A3,"Market cap",TRUE)</f>
-        <v>15944032</v>
+        <v>17177314</v>
       </c>
       <c r="C3" s="109" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Price")</f>
-        <v>6.5000000000000002E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D3" s="1" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(A3,"Shares outstanding",TRUE)</f>
-        <v>245292800</v>
+        <v>245390200</v>
       </c>
       <c r="E3" s="48">
         <v>1024293</v>
@@ -58814,11 +58973,11 @@
       </c>
       <c r="C8" s="24">
         <f ca="1">B8*I1</f>
-        <v>4599285.1100000003</v>
+        <v>4995804.84</v>
       </c>
       <c r="D8" s="74">
         <f ca="1">C8/B3</f>
-        <v>0.28846436773333123</v>
+        <v>0.29083737073211796</v>
       </c>
       <c r="E8">
         <v>9.4</v>
@@ -58994,7 +59153,7 @@
       </c>
       <c r="J18" s="90">
         <f ca="1">B8*I1</f>
-        <v>4599285.1100000003</v>
+        <v>4995804.84</v>
       </c>
       <c r="K18" s="24">
         <f>E3</f>
@@ -59002,7 +59161,7 @@
       </c>
       <c r="L18" s="46">
         <f ca="1">SUM(B18:K18)</f>
-        <v>27518578.109999999</v>
+        <v>27915097.84</v>
       </c>
       <c r="M18" s="50">
         <f>F3</f>
@@ -59010,7 +59169,7 @@
       </c>
       <c r="N18" s="66">
         <f ca="1">(L18-M18)/B3</f>
-        <v>1.1491437742974926</v>
+        <v>1.0897224583540825</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="21" x14ac:dyDescent="0.25">
@@ -59129,7 +59288,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75639D07-9CE4-4547-8AAF-982CD8A8A363}">
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -59565,7 +59724,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="104">
         <v>45292</v>
       </c>
@@ -59603,7 +59762,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>12.4</v>
       </c>
@@ -59641,12 +59800,12 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="104">
         <v>45292</v>
       </c>
@@ -59684,7 +59843,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="82">
         <v>2.1</v>
       </c>
@@ -59722,12 +59881,12 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="104">
         <v>45292</v>
       </c>
@@ -59765,7 +59924,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7648</v>
       </c>
@@ -59803,12 +59962,12 @@
         <v>17722</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="104">
         <v>45292</v>
       </c>
@@ -59846,7 +60005,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41.9</v>
       </c>
@@ -59884,17 +60043,17 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="104">
         <v>45292</v>
       </c>
@@ -59931,8 +60090,23 @@
       <c r="L47" s="104">
         <v>45627</v>
       </c>
+      <c r="M47" s="104">
+        <v>45658</v>
+      </c>
+      <c r="N47" s="104">
+        <v>45689</v>
+      </c>
+      <c r="O47" s="104">
+        <v>45717</v>
+      </c>
+      <c r="P47" s="104">
+        <v>45748</v>
+      </c>
+      <c r="Q47" s="104">
+        <v>45778</v>
+      </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>6.2</v>
       </c>
@@ -59969,13 +60143,28 @@
       <c r="L48">
         <v>31</v>
       </c>
+      <c r="M48">
+        <v>31</v>
+      </c>
+      <c r="N48">
+        <v>31</v>
+      </c>
+      <c r="O48">
+        <v>37</v>
+      </c>
+      <c r="P48">
+        <v>40</v>
+      </c>
+      <c r="Q48">
+        <v>41</v>
+      </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="104">
         <v>45292</v>
       </c>
@@ -60012,8 +60201,23 @@
       <c r="L50" s="104">
         <v>45650</v>
       </c>
+      <c r="M50" s="104">
+        <v>45681</v>
+      </c>
+      <c r="N50" s="104">
+        <v>45712</v>
+      </c>
+      <c r="O50" s="104">
+        <v>45740</v>
+      </c>
+      <c r="P50" s="104">
+        <v>45771</v>
+      </c>
+      <c r="Q50" s="104">
+        <v>45801</v>
+      </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="82">
         <v>2.5</v>
       </c>
@@ -60050,13 +60254,28 @@
       <c r="L51" s="82">
         <v>1.6</v>
       </c>
+      <c r="M51" s="82">
+        <v>1.7</v>
+      </c>
+      <c r="N51" s="82">
+        <v>1.3</v>
+      </c>
+      <c r="O51" s="82">
+        <v>1.4</v>
+      </c>
+      <c r="P51" s="82">
+        <v>1.6</v>
+      </c>
+      <c r="Q51" s="82">
+        <v>1.6</v>
+      </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="104">
         <v>45292</v>
       </c>
@@ -60093,8 +60312,23 @@
       <c r="L53" s="104">
         <v>45650</v>
       </c>
+      <c r="M53" s="104">
+        <v>45681</v>
+      </c>
+      <c r="N53" s="104">
+        <v>45712</v>
+      </c>
+      <c r="O53" s="104">
+        <v>45740</v>
+      </c>
+      <c r="P53" s="104">
+        <v>45771</v>
+      </c>
+      <c r="Q53" s="104">
+        <v>45801</v>
+      </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>60.4</v>
       </c>
@@ -60130,6 +60364,21 @@
       </c>
       <c r="L54">
         <v>18.8</v>
+      </c>
+      <c r="M54">
+        <v>18</v>
+      </c>
+      <c r="N54">
+        <v>16</v>
+      </c>
+      <c r="O54">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="P54">
+        <v>15.8</v>
+      </c>
+      <c r="Q54">
+        <v>16.3</v>
       </c>
     </row>
   </sheetData>
@@ -60205,7 +60454,7 @@
       </c>
       <c r="M3" s="21" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">_FV(L3,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="O3" s="83"/>
       <c r="P3" s="81" t="s">
@@ -60219,15 +60468,15 @@
       </c>
       <c r="B4" s="15" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">_FV(A4,"Market cap",TRUE)</f>
-        <v>2789418157</v>
+        <v>2282747013</v>
       </c>
       <c r="C4" s="14" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">_FV(A4,"Price")</f>
-        <v>13.01</v>
+        <v>10.17</v>
       </c>
       <c r="D4" s="1" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">_FV(A4,"Shares outstanding",TRUE)</f>
-        <v>214405700</v>
+        <v>224458900</v>
       </c>
       <c r="E4" s="48">
         <v>425300000</v>
@@ -60243,7 +60492,7 @@
       </c>
       <c r="M4" s="21" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">_FV(L4,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="O4" s="67"/>
       <c r="P4" s="16" t="s">
@@ -60259,15 +60508,15 @@
       </c>
       <c r="B5" s="15" cm="1">
         <f t="array" aca="1" ref="B5" ca="1">_FV(A5,"Market cap",TRUE)</f>
-        <v>3110795152</v>
+        <v>2614756998</v>
       </c>
       <c r="C5" s="14" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(A5,"Price")</f>
-        <v>16.16</v>
+        <v>13.29</v>
       </c>
       <c r="D5" s="1" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">_FV(A5,"Shares outstanding",TRUE)</f>
-        <v>192499700</v>
+        <v>196746200</v>
       </c>
       <c r="E5" s="48">
         <v>203900000</v>
@@ -60293,15 +60542,15 @@
       </c>
       <c r="B6" s="15" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">_FV(A6,"Market cap",TRUE)</f>
-        <v>472808952</v>
+        <v>540230340</v>
       </c>
       <c r="C6" s="14" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(A6,"Price")</f>
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="D6" s="1" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">_FV(A6,"Shares outstanding",TRUE)</f>
-        <v>153509400</v>
+        <v>207780900</v>
       </c>
       <c r="E6" s="48">
         <v>35500000</v>
@@ -60332,15 +60581,15 @@
       </c>
       <c r="B7" s="15" cm="1">
         <f t="array" aca="1" ref="B7" ca="1">_FV(A7,"Market cap",TRUE)</f>
-        <v>1871652344</v>
+        <v>1632166602</v>
       </c>
       <c r="C7" s="14" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(A7,"Price")</f>
-        <v>4.8499999999999996</v>
+        <v>4.26</v>
       </c>
       <c r="D7" s="1" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">_FV(A7,"Shares outstanding",TRUE)</f>
-        <v>385907700</v>
+        <v>383137700</v>
       </c>
       <c r="E7" s="48">
         <v>104100000</v>
@@ -60374,15 +60623,15 @@
       </c>
       <c r="B8" s="15" cm="1">
         <f t="array" aca="1" ref="B8" ca="1">_FV(A8,"Market cap",TRUE)</f>
-        <v>2954095952</v>
+        <v>2727964298</v>
       </c>
       <c r="C8" s="14" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(A8,"Price")</f>
-        <v>10.52</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="D8" s="1" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">_FV(A8,"Shares outstanding",TRUE)</f>
-        <v>280807600</v>
+        <v>280943800</v>
       </c>
       <c r="E8" s="48">
         <v>328400000</v>
@@ -60413,15 +60662,15 @@
       </c>
       <c r="B9" s="15" cm="1">
         <f t="array" aca="1" ref="B9" ca="1">_FV(A9,"Market cap",TRUE)</f>
-        <v>3376168770</v>
+        <v>3615556652</v>
       </c>
       <c r="C9" s="14" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(A9,"Price")</f>
-        <v>12.09</v>
+        <v>12.14</v>
       </c>
       <c r="D9" s="1" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">_FV(A9,"Shares outstanding",TRUE)</f>
-        <v>279253000</v>
+        <v>297821800</v>
       </c>
       <c r="E9" s="48">
         <v>98000000</v>
@@ -60447,15 +60696,15 @@
       </c>
       <c r="B10" s="15" cm="1">
         <f t="array" aca="1" ref="B10" ca="1">_FV(A10,"Market cap",TRUE)</f>
-        <v>580442400</v>
+        <v>513033200</v>
       </c>
       <c r="C10" s="14" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(A10,"Price")</f>
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="D10" s="1" cm="1">
         <f t="array" aca="1" ref="D10" ca="1">_FV(A10,"Shares outstanding",TRUE)</f>
-        <v>148072000</v>
+        <v>187238400</v>
       </c>
       <c r="E10" s="48">
         <v>9600000</v>
@@ -60477,15 +60726,15 @@
       </c>
       <c r="B11" s="15" cm="1">
         <f t="array" aca="1" ref="B11" ca="1">_FV(A11,"Market cap",TRUE)</f>
-        <v>2028835488</v>
+        <v>1287444096</v>
       </c>
       <c r="C11" s="14" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(A11,"Price")</f>
-        <v>5.78</v>
+        <v>3.84</v>
       </c>
       <c r="D11" s="1" cm="1">
         <f t="array" aca="1" ref="D11" ca="1">_FV(A11,"Shares outstanding",TRUE)</f>
-        <v>351009600</v>
+        <v>335271900</v>
       </c>
       <c r="E11" s="48">
         <v>96000000</v>
@@ -60500,15 +60749,15 @@
       </c>
       <c r="B12" s="15" cm="1">
         <f t="array" aca="1" ref="B12" ca="1">_FV(A12,"Market cap",TRUE)</f>
-        <v>851518400</v>
+        <v>683832800</v>
       </c>
       <c r="C12" s="14" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(A12,"Price")</f>
-        <v>1.36</v>
+        <v>0.87</v>
       </c>
       <c r="D12" s="1" cm="1">
         <f t="array" aca="1" ref="D12" ca="1">_FV(A12,"Shares outstanding",TRUE)</f>
-        <v>452935300</v>
+        <v>555961600</v>
       </c>
       <c r="E12" s="48">
         <v>66000000</v>
@@ -60557,11 +60806,11 @@
       </c>
       <c r="C16" s="24">
         <f ca="1">B16*$M$3</f>
-        <v>693024194.66000009</v>
+        <v>752772125.03999996</v>
       </c>
       <c r="D16" s="74">
         <f ca="1">C16/B4</f>
-        <v>0.24844758141437742</v>
+        <v>0.32976590079980095</v>
       </c>
       <c r="E16">
         <v>400</v>
@@ -60603,7 +60852,7 @@
       </c>
       <c r="C18" s="24">
         <f ca="1">B18*$M$3</f>
-        <v>41002137.469999999</v>
+        <v>44537068.68</v>
       </c>
       <c r="D18" s="74">
         <v>0</v>
@@ -60650,11 +60899,11 @@
       </c>
       <c r="C20" s="24">
         <f t="shared" ref="C20:C24" ca="1" si="1">B20*$M$3</f>
-        <v>93551416.280000001</v>
+        <v>101616796.32000001</v>
       </c>
       <c r="D20" s="74">
         <f ca="1">C20/B6</f>
-        <v>0.19786303936140362</v>
+        <v>0.18809901776342292</v>
       </c>
       <c r="E20" s="68">
         <v>90</v>
@@ -60703,11 +60952,11 @@
       </c>
       <c r="C22" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>244251396.48000002</v>
+        <v>265309125.12</v>
       </c>
       <c r="D22" s="74">
         <f ca="1">C22/B10</f>
-        <v>0.42080212692939045</v>
+        <v>0.51713831603880611</v>
       </c>
       <c r="E22" s="68">
         <v>142</v>
@@ -60726,11 +60975,11 @@
       </c>
       <c r="C23" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>198943545.29000002</v>
+        <v>216095132.75999999</v>
       </c>
       <c r="D23" s="74">
         <f ca="1">C23/B11</f>
-        <v>9.8057997539325384E-2</v>
+        <v>0.16784816787881715</v>
       </c>
       <c r="E23" s="68">
         <v>236</v>
@@ -60748,11 +60997,11 @@
       </c>
       <c r="C24" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>88560702.650000006</v>
+        <v>96195816.599999994</v>
       </c>
       <c r="D24" s="74">
         <f ca="1">C24/B12</f>
-        <v>0.10400327538430175</v>
+        <v>0.14067154514963306</v>
       </c>
       <c r="E24" s="68">
         <v>240</v>
@@ -61157,7 +61406,7 @@
       </c>
       <c r="J40" s="90">
         <f ca="1">C16</f>
-        <v>693024194.66000009</v>
+        <v>752772125.03999996</v>
       </c>
       <c r="K40" s="90">
         <v>0</v>
@@ -61167,7 +61416,7 @@
       </c>
       <c r="M40" s="46">
         <f t="shared" ref="M40:M45" ca="1" si="5">SUM(B40:L40)</f>
-        <v>1910424194.6600001</v>
+        <v>1970172125.04</v>
       </c>
       <c r="N40" s="50">
         <f>F8</f>
@@ -61175,7 +61424,7 @@
       </c>
       <c r="O40" s="66">
         <f ca="1">(M40-N40)/B8</f>
-        <v>0.62185664396455598</v>
+        <v>0.69530679944404461</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
@@ -61232,7 +61481,7 @@
       </c>
       <c r="O41" s="66">
         <f ca="1">(M41-N41)/B4</f>
-        <v>0.82010651370403331</v>
+        <v>1.0021347030451684</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
@@ -61268,7 +61517,7 @@
       </c>
       <c r="J42" s="90">
         <f t="shared" ca="1" si="6"/>
-        <v>41002137.469999999</v>
+        <v>44537068.68</v>
       </c>
       <c r="K42" s="90">
         <v>0</v>
@@ -61279,7 +61528,7 @@
       </c>
       <c r="M42" s="46">
         <f t="shared" ca="1" si="5"/>
-        <v>1152672137.47</v>
+        <v>1156207068.6799998</v>
       </c>
       <c r="N42" s="50">
         <f>F5</f>
@@ -61287,7 +61536,7 @@
       </c>
       <c r="O42" s="66">
         <f ca="1">(M42-N42)/B5</f>
-        <v>0.35838815575921923</v>
+        <v>0.42772887481913524</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
@@ -61342,7 +61591,7 @@
       </c>
       <c r="O43" s="66">
         <f ca="1">(M43-N43)/B7</f>
-        <v>0.32167191836135139</v>
+        <v>0.36887043225995381</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
@@ -61377,11 +61626,11 @@
       </c>
       <c r="J44" s="90">
         <f ca="1">C20</f>
-        <v>93551416.280000001</v>
+        <v>101616796.32000001</v>
       </c>
       <c r="K44" s="90">
         <f ca="1">depth!B67</f>
-        <v>44027698.710000001</v>
+        <v>42524632.149999999</v>
       </c>
       <c r="L44" s="24">
         <f>E6</f>
@@ -61389,7 +61638,7 @@
       </c>
       <c r="M44" s="46">
         <f t="shared" ca="1" si="5"/>
-        <v>266649114.99000001</v>
+        <v>273211428.47000003</v>
       </c>
       <c r="N44" s="50">
         <f>F6</f>
@@ -61397,7 +61646,7 @@
       </c>
       <c r="O44" s="66">
         <f ca="1">(M44-N44)/B6</f>
-        <v>0.56396799143092369</v>
+        <v>0.50573136723494649</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
@@ -61452,7 +61701,7 @@
       </c>
       <c r="O45" s="66">
         <f ca="1">(M45-N45)/B7</f>
-        <v>0.84789785084147018</v>
+        <v>0.97230883051729056</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -61488,7 +61737,7 @@
       </c>
       <c r="J46" s="90">
         <f ca="1">C22</f>
-        <v>244251396.48000002</v>
+        <v>265309125.12</v>
       </c>
       <c r="K46" s="90">
         <v>0</v>
@@ -61499,7 +61748,7 @@
       </c>
       <c r="M46" s="46">
         <f ca="1">SUM(B46:L46)</f>
-        <v>617051396.48000002</v>
+        <v>638109125.12</v>
       </c>
       <c r="N46" s="50">
         <f>F10</f>
@@ -61507,7 +61756,7 @@
       </c>
       <c r="O46" s="66">
         <f ca="1">(M46-N46)/B10</f>
-        <v>1.000118868780089</v>
+        <v>1.1725734808585488</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
@@ -61543,7 +61792,7 @@
       </c>
       <c r="J47" s="90">
         <f ca="1">C23</f>
-        <v>198943545.29000002</v>
+        <v>216095132.75999999</v>
       </c>
       <c r="K47" s="90">
         <v>0</v>
@@ -61554,7 +61803,7 @@
       </c>
       <c r="M47" s="46">
         <f ca="1">SUM(B47:L47)</f>
-        <v>607323545.28999996</v>
+        <v>624475132.75999999</v>
       </c>
       <c r="N47" s="50">
         <f>F11</f>
@@ -61562,7 +61811,7 @@
       </c>
       <c r="O47" s="66">
         <f ca="1">(M47-N47)/B11</f>
-        <v>0.25158449184717729</v>
+        <v>0.40978488650430689</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
@@ -61598,7 +61847,7 @@
       </c>
       <c r="J48" s="90">
         <f ca="1">C24</f>
-        <v>88560702.650000006</v>
+        <v>96195816.599999994</v>
       </c>
       <c r="K48" s="90">
         <v>0</v>
@@ -61609,7 +61858,7 @@
       </c>
       <c r="M48" s="46">
         <f ca="1">SUM(B48:L48)</f>
-        <v>705320702.64999998</v>
+        <v>712955816.60000002</v>
       </c>
       <c r="N48" s="50">
         <f>F12</f>
@@ -61617,7 +61866,7 @@
       </c>
       <c r="O48" s="66">
         <f ca="1">(M48-N48)/B12</f>
-        <v>0.82830940899221905</v>
+        <v>1.0425879200295745</v>
       </c>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.2">
@@ -61781,15 +62030,15 @@
       </c>
       <c r="B3" s="24" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A3,"Market cap",TRUE)</f>
-        <v>580442400</v>
+        <v>513033200</v>
       </c>
       <c r="C3" s="57" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Price")</f>
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="D3" s="1" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(A3,"Shares outstanding",TRUE)</f>
-        <v>148072000</v>
+        <v>187238400</v>
       </c>
       <c r="E3" s="48">
         <v>25600000</v>
@@ -61802,7 +62051,7 @@
       </c>
       <c r="M3" s="21" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">_FV(L3,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="P3" s="81" t="s">
         <v>111</v>
@@ -61818,7 +62067,7 @@
       </c>
       <c r="M4" s="21" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">_FV(L4,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="P4" s="16" t="s">
         <v>124</v>
@@ -61893,11 +62142,11 @@
       </c>
       <c r="C8" s="90">
         <f t="shared" ref="C8" ca="1" si="0">B8*$M$3</f>
-        <v>247872110.29000002</v>
+        <v>269241992.75999999</v>
       </c>
       <c r="D8" s="105">
         <f ca="1">C8/B3</f>
-        <v>0.42703997897121232</v>
+        <v>0.52480422857624032</v>
       </c>
       <c r="E8" s="68">
         <v>142</v>
@@ -62082,7 +62331,7 @@
       </c>
       <c r="J18" s="90">
         <f ca="1">C8</f>
-        <v>247872110.29000002</v>
+        <v>269241992.75999999</v>
       </c>
       <c r="K18" s="90">
         <v>0</v>
@@ -62093,7 +62342,7 @@
       </c>
       <c r="M18" s="46">
         <f ca="1">SUM(B18:L18)</f>
-        <v>794282110.28999996</v>
+        <v>815651992.75999999</v>
       </c>
       <c r="N18" s="50">
         <f>F3</f>
@@ -62101,7 +62350,7 @@
       </c>
       <c r="O18" s="66">
         <f ca="1">(M18-N18)/B3</f>
-        <v>1.2884674005379344</v>
+        <v>1.4994175674400798</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
@@ -62237,15 +62486,15 @@
       </c>
       <c r="B3" s="90" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A3,"Market cap",TRUE)</f>
-        <v>2107698096</v>
+        <v>1931409000</v>
       </c>
       <c r="C3" s="82" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Price")</f>
-        <v>20.32</v>
+        <v>18.36</v>
       </c>
       <c r="D3" s="1" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(A3,"Shares outstanding",TRUE)</f>
-        <v>103725300</v>
+        <v>104169300</v>
       </c>
       <c r="E3" s="48">
         <v>175476000</v>
@@ -62258,7 +62507,7 @@
       </c>
       <c r="M3" s="21" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">_FV(L3,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="P3" s="81" t="s">
         <v>111</v>
@@ -62274,7 +62523,7 @@
       </c>
       <c r="M4" s="21" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">_FV(L4,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="P4" s="16" t="s">
         <v>124</v>
@@ -62352,11 +62601,11 @@
       </c>
       <c r="C8" s="14">
         <f ca="1">B8*$M$3</f>
-        <v>890695597.25999999</v>
+        <v>967485439.44000006</v>
       </c>
       <c r="D8" s="106">
         <f ca="1">C8/B3</f>
-        <v>0.42259164106584646</v>
+        <v>0.50092209337328342</v>
       </c>
       <c r="E8">
         <v>182</v>
@@ -62544,7 +62793,7 @@
       </c>
       <c r="J18" s="90">
         <f ca="1">C8</f>
-        <v>890695597.25999999</v>
+        <v>967485439.44000006</v>
       </c>
       <c r="K18" s="90">
         <v>0</v>
@@ -62555,7 +62804,7 @@
       </c>
       <c r="M18" s="46">
         <f ca="1">SUM(B18:L18)</f>
-        <v>1636021597.26</v>
+        <v>1712811439.4400001</v>
       </c>
       <c r="N18" s="50">
         <f>F3</f>
@@ -62563,7 +62812,7 @@
       </c>
       <c r="O18" s="66">
         <f ca="1">(M18-N18)/B3</f>
-        <v>0.57758110593273504</v>
+        <v>0.67005820074360223</v>
       </c>
     </row>
   </sheetData>
@@ -62668,7 +62917,7 @@
       </c>
       <c r="I1" s="21" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_FV(H1,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="K1" s="81" t="s">
         <v>111</v>
@@ -62697,7 +62946,7 @@
       </c>
       <c r="I2" s="21" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">_FV(H2,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>124</v>
@@ -62712,15 +62961,15 @@
       </c>
       <c r="B3" s="15" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A3,"Market cap",TRUE)</f>
-        <v>1871652344</v>
+        <v>1632166602</v>
       </c>
       <c r="C3" s="14" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Price")</f>
-        <v>4.8499999999999996</v>
+        <v>4.26</v>
       </c>
       <c r="D3" s="1" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(A3,"Shares outstanding",TRUE)</f>
-        <v>385907700</v>
+        <v>383137700</v>
       </c>
       <c r="E3" s="48">
         <v>104100000</v>
@@ -63019,7 +63268,7 @@
       </c>
       <c r="N18" s="66">
         <f ca="1">(L18-M18)/B3</f>
-        <v>0.47046130272150583</v>
+        <v>0.53949149487620751</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -63169,7 +63418,7 @@
       </c>
       <c r="I1" s="21" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_FV(H1,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="K1" s="81" t="s">
         <v>111</v>
@@ -63198,7 +63447,7 @@
       </c>
       <c r="I2" s="21" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">_FV(H2,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>124</v>
@@ -63213,15 +63462,15 @@
       </c>
       <c r="B3" s="15" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A3,"Market cap",TRUE)</f>
-        <v>2028835488</v>
+        <v>1287444096</v>
       </c>
       <c r="C3" s="14" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Price")</f>
-        <v>5.78</v>
+        <v>3.84</v>
       </c>
       <c r="D3" s="1" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(A3,"Shares outstanding",TRUE)</f>
-        <v>351009600</v>
+        <v>335271900</v>
       </c>
       <c r="E3" s="48">
         <v>122557000</v>
@@ -63312,11 +63561,11 @@
       </c>
       <c r="C8" s="24">
         <f ca="1">B8*I1</f>
-        <v>222135685.10000002</v>
+        <v>241286744.40000001</v>
       </c>
       <c r="D8" s="74">
         <f ca="1">C8/B3</f>
-        <v>0.10948925450775633</v>
+        <v>0.18741531779877765</v>
       </c>
       <c r="E8" s="68">
         <v>266</v>
@@ -63492,7 +63741,7 @@
       </c>
       <c r="J18" s="90">
         <f ca="1">C8</f>
-        <v>222135685.10000002</v>
+        <v>241286744.40000001</v>
       </c>
       <c r="K18" s="24">
         <f>E3</f>
@@ -63500,7 +63749,7 @@
       </c>
       <c r="L18" s="46">
         <f ca="1">SUM(B18:K18)</f>
-        <v>1417922685.0999999</v>
+        <v>1437073744.4000001</v>
       </c>
       <c r="M18" s="50">
         <f>F3</f>
@@ -63508,7 +63757,7 @@
       </c>
       <c r="N18" s="66">
         <f ca="1">(L18-M18)/B3</f>
-        <v>0.65707727067321486</v>
+        <v>1.0503390000399677</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
@@ -63621,7 +63870,7 @@
       </c>
       <c r="I1" s="21" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_FV(H1,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="K1" s="81" t="s">
         <v>111</v>
@@ -63646,14 +63895,14 @@
         <v>71</v>
       </c>
       <c r="G2" s="77" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H2" s="45" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="I2" s="21" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">_FV(H2,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>124</v>
@@ -63668,15 +63917,15 @@
       </c>
       <c r="B3" s="15" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A3,"Market cap",TRUE)</f>
-        <v>3838226436</v>
+        <v>3647662377</v>
       </c>
       <c r="C3" s="14" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Price")</f>
-        <v>11.16</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="D3" s="1" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(A3,"Shares outstanding",TRUE)</f>
-        <v>343927100</v>
+        <v>357263700</v>
       </c>
       <c r="E3" s="48">
         <v>355000000</v>
@@ -63686,7 +63935,7 @@
       </c>
       <c r="G3" s="28">
         <f ca="1">C41*B41</f>
-        <v>122550840.32000001</v>
+        <v>78396493.439999998</v>
       </c>
       <c r="K3" s="16" t="s">
         <v>142</v>
@@ -63750,7 +63999,7 @@
         <v>84</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F7" s="71" t="s">
         <v>108</v>
@@ -63774,11 +64023,11 @@
       </c>
       <c r="C8" s="24">
         <f ca="1">B8*I1</f>
-        <v>1734224057.8600001</v>
+        <v>1883737305.8399999</v>
       </c>
       <c r="D8" s="74">
         <f ca="1">C8/B3</f>
-        <v>0.45182953293066219</v>
+        <v>0.51642315300827524</v>
       </c>
       <c r="E8">
         <v>800</v>
@@ -63864,7 +64113,7 @@
       </c>
       <c r="M13" s="114">
         <f ca="1">L18-M18</f>
-        <v>3754709898.1800003</v>
+        <v>3860068799.2800002</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="24" x14ac:dyDescent="0.3">
@@ -63887,7 +64136,7 @@
       <c r="O16" s="80"/>
     </row>
     <row r="17" spans="1:15" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="119"/>
+      <c r="A17" s="115"/>
       <c r="B17" s="86" t="s">
         <v>94</v>
       </c>
@@ -63928,7 +64177,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="87" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
@@ -63964,7 +64213,7 @@
       </c>
       <c r="J18" s="90">
         <f ca="1">B8*I1</f>
-        <v>1734224057.8600001</v>
+        <v>1883737305.8399999</v>
       </c>
       <c r="K18" s="24">
         <f>E3</f>
@@ -63972,19 +64221,19 @@
       </c>
       <c r="L18" s="46">
         <f ca="1">(SUM(B18:K18))+G3</f>
-        <v>3927709898.1800003</v>
+        <v>4033068799.2800002</v>
       </c>
       <c r="M18" s="50">
         <f>F3</f>
         <v>173000000</v>
       </c>
-      <c r="N18" s="121">
+      <c r="N18" s="117">
         <f ca="1">(L18-M18)/B3</f>
-        <v>0.97824085180679532</v>
-      </c>
-      <c r="O18" s="121">
+        <v>1.0582308339772095</v>
+      </c>
+      <c r="O18" s="117">
         <f ca="1">M13/D3</f>
-        <v>10.917167906163836</v>
+        <v>10.804536814907308</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
@@ -63996,7 +64245,7 @@
         <v>148</v>
       </c>
       <c r="D40" s="77" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
@@ -64005,26 +64254,26 @@
       </c>
       <c r="B41" s="14" cm="1">
         <f t="array" aca="1" ref="B41" ca="1">_FV(A41,"Price")</f>
-        <v>1.36</v>
+        <v>0.87</v>
       </c>
       <c r="C41" s="1">
         <v>90110912</v>
       </c>
-      <c r="D41" s="120">
+      <c r="D41" s="116">
         <f ca="1">C41*B41</f>
-        <v>122550840.32000001</v>
+        <v>78396493.439999998</v>
       </c>
     </row>
     <row r="42" spans="1:21" s="112" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="44" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A44" s="126" t="s">
-        <v>175</v>
-      </c>
-      <c r="P44" s="125"/>
+      <c r="A44" s="121" t="s">
+        <v>171</v>
+      </c>
+      <c r="P44" s="120"/>
     </row>
     <row r="45" spans="1:21" ht="24" x14ac:dyDescent="0.3">
       <c r="A45" s="72" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B45" s="72"/>
       <c r="C45" s="72"/>
@@ -64037,20 +64286,20 @@
       </c>
       <c r="I45" s="21" cm="1">
         <f t="array" aca="1" ref="I45" ca="1">_FV(H45,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="K45" s="81" t="s">
         <v>111</v>
       </c>
       <c r="L45" s="79"/>
       <c r="P45" s="56" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q45" s="127" t="s">
-        <v>172</v>
+        <v>170</v>
+      </c>
+      <c r="Q45" s="122" t="s">
+        <v>168</v>
       </c>
       <c r="R45" s="56" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="S45" s="56"/>
       <c r="T45" s="56"/>
@@ -64074,14 +64323,14 @@
         <v>71</v>
       </c>
       <c r="G46" s="77" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H46" s="45" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="I46" s="21" cm="1">
         <f t="array" aca="1" ref="I46" ca="1">_FV(H46,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="K46" s="16" t="s">
         <v>124</v>
@@ -64090,14 +64339,14 @@
         <v>30000</v>
       </c>
       <c r="P46" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="90">
         <v>500000000</v>
       </c>
-      <c r="R46" s="124">
+      <c r="R46" s="119">
         <f ca="1">Q46/$C$47</f>
-        <v>44802867.383512542</v>
+        <v>48971596.474045053</v>
       </c>
       <c r="S46" s="1"/>
       <c r="T46" s="66"/>
@@ -64108,15 +64357,15 @@
       </c>
       <c r="B47" s="15" cm="1">
         <f t="array" aca="1" ref="B47" ca="1">_FV(A47,"Market cap",TRUE)</f>
-        <v>3838226436</v>
+        <v>3647662377</v>
       </c>
       <c r="C47" s="14" cm="1">
         <f t="array" aca="1" ref="C47" ca="1">_FV(A47,"Price")</f>
-        <v>11.16</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="D47" s="1" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">_FV(A47,"Shares outstanding",TRUE) + IF(A44="None", 0, VLOOKUP(A44, P46:R49, 3, FALSE))</f>
-        <v>343927100</v>
+        <v>357263700</v>
       </c>
       <c r="E47" s="48">
         <f>355000000</f>
@@ -64127,7 +64376,7 @@
       </c>
       <c r="G47" s="28">
         <f ca="1">B41*C41</f>
-        <v>122550840.32000001</v>
+        <v>78396493.439999998</v>
       </c>
       <c r="K47" s="16" t="s">
         <v>142</v>
@@ -64136,14 +64385,14 @@
         <v>300000</v>
       </c>
       <c r="P47" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q47" s="90">
         <v>1000000000</v>
       </c>
-      <c r="R47" s="124">
+      <c r="R47" s="119">
         <f t="shared" ref="R47" ca="1" si="0">Q47/$C$47</f>
-        <v>89605734.767025083</v>
+        <v>97943192.948090106</v>
       </c>
       <c r="S47" s="1"/>
       <c r="T47" s="66"/>
@@ -64156,14 +64405,14 @@
         <v>750000</v>
       </c>
       <c r="P48" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Q48" s="90">
         <v>1500000000</v>
       </c>
-      <c r="R48" s="124">
+      <c r="R48" s="119">
         <f ca="1">Q48/$C$47</f>
-        <v>134408602.15053764</v>
+        <v>146914789.42213514</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="66"/>
@@ -64180,7 +64429,7 @@
         <v>1500000</v>
       </c>
       <c r="P49" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="Q49" s="90">
         <v>0</v>
@@ -64225,7 +64474,7 @@
         <v>84</v>
       </c>
       <c r="E51" s="77" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F51" s="71" t="s">
         <v>108</v>
@@ -64234,7 +64483,7 @@
         <v>78</v>
       </c>
       <c r="H51" s="77" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I51" s="16" t="s">
         <v>103</v>
@@ -64252,11 +64501,11 @@
       </c>
       <c r="C52" s="24">
         <f ca="1">B52*I45</f>
-        <v>1734224057.8600001</v>
+        <v>1883737305.8399999</v>
       </c>
       <c r="D52" s="74">
         <f ca="1">C52/B47</f>
-        <v>0.45182953293066219</v>
+        <v>0.51642315300827524</v>
       </c>
       <c r="E52">
         <v>800</v>
@@ -64364,7 +64613,7 @@
       <c r="O60" s="80"/>
     </row>
     <row r="61" spans="1:18" ht="51" x14ac:dyDescent="0.2">
-      <c r="A61" s="119"/>
+      <c r="A61" s="115"/>
       <c r="B61" s="86" t="s">
         <v>94</v>
       </c>
@@ -64405,7 +64654,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="87" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
@@ -64423,7 +64672,7 @@
         <f>F52*L48</f>
         <v>870000000</v>
       </c>
-      <c r="E62" s="122">
+      <c r="E62" s="118">
         <f>H52*L50</f>
         <v>1500000000</v>
       </c>
@@ -64442,7 +64691,7 @@
       </c>
       <c r="J62" s="90">
         <f ca="1">B52*I45</f>
-        <v>1734224057.8600001</v>
+        <v>1883737305.8399999</v>
       </c>
       <c r="K62" s="24">
         <f>E47</f>
@@ -64450,25 +64699,25 @@
       </c>
       <c r="L62" s="46">
         <f ca="1">(SUM(B62:K62))+G47</f>
-        <v>5427709898.1800003</v>
+        <v>5533068799.2799997</v>
       </c>
       <c r="M62" s="50">
         <f>F47</f>
         <v>173000000</v>
       </c>
-      <c r="N62" s="121">
+      <c r="N62" s="117">
         <f ca="1">(L62-M62)/B47</f>
-        <v>1.3690463514331337</v>
-      </c>
-      <c r="O62" s="121">
+        <v>1.4694531031921763</v>
+      </c>
+      <c r="O62" s="117">
         <f ca="1">N66/D47</f>
-        <v>15.278557281993772</v>
+        <v>15.00311618359212</v>
       </c>
     </row>
     <row r="66" spans="14:14" x14ac:dyDescent="0.2">
       <c r="N66" s="114">
         <f ca="1">L62-M62</f>
-        <v>5254709898.1800003</v>
+        <v>5360068799.2799997</v>
       </c>
     </row>
   </sheetData>
@@ -64672,7 +64921,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D911E8-57A6-CB44-8AD4-C1D490A2590F}">
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
@@ -64680,11 +64929,10 @@
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.83203125" customWidth="1"/>
     <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.5" bestFit="1" customWidth="1"/>
@@ -64693,20 +64941,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
       <c r="H1" s="20" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="I1" s="21" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_FV(H1,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="K1" s="81" t="s">
         <v>111</v>
@@ -64735,7 +64983,7 @@
       </c>
       <c r="I2" s="21" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">_FV(H2,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>124</v>
@@ -64751,22 +64999,23 @@
       </c>
       <c r="B3" s="28">
         <f ca="1">C3*D3</f>
-        <v>2789418157</v>
+        <v>2282747013</v>
       </c>
       <c r="C3" s="14" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Price")</f>
-        <v>13.01</v>
+        <v>10.17</v>
       </c>
       <c r="D3" s="1" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(A3,"Shares outstanding",TRUE)</f>
-        <v>214405700</v>
+        <v>224458900</v>
       </c>
       <c r="E3" s="48">
-        <v>427000000</v>
+        <v>184000000</v>
       </c>
       <c r="F3" s="58">
-        <v>151663000</v>
-      </c>
+        <v>1056000000</v>
+      </c>
+      <c r="G3" s="24"/>
       <c r="K3" s="16" t="s">
         <v>142</v>
       </c>
@@ -64809,7 +65058,7 @@
         <v>102</v>
       </c>
       <c r="I6" s="82">
-        <v>17.489999999999998</v>
+        <v>17.77</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>121</v>
@@ -64829,7 +65078,7 @@
         <v>84</v>
       </c>
       <c r="E7" s="71" t="s">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="F7" s="77" t="s">
         <v>78</v>
@@ -64841,7 +65090,7 @@
         <v>103</v>
       </c>
       <c r="I7" s="82">
-        <v>12.68</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -64860,7 +65109,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>460</v>
+        <v>660</v>
       </c>
       <c r="F8">
         <v>3150</v>
@@ -64872,7 +65121,7 @@
         <v>104</v>
       </c>
       <c r="I8" s="82">
-        <v>3.37</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -64897,7 +65146,6 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B12" s="71" t="s">
@@ -64918,9 +65166,6 @@
       <c r="G12" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="H12" s="77" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="60" t="e" vm="1">
@@ -64928,26 +65173,23 @@
       </c>
       <c r="B13" s="89">
         <f>(E8*1000000)/(F13*1000000)</f>
-        <v>14.838709677419354</v>
+        <v>16.097560975609756</v>
       </c>
       <c r="C13" s="69">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="D13" s="1">
-        <v>76105</v>
+        <v>92900</v>
       </c>
       <c r="E13" s="84">
         <f>(F13*1000000)/D13</f>
-        <v>407.33197556008145</v>
+        <v>441.33476856835307</v>
       </c>
       <c r="F13">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G13">
         <v>50</v>
-      </c>
-      <c r="H13">
-        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="24" x14ac:dyDescent="0.3">
@@ -64967,7 +65209,6 @@
       <c r="L16" s="80"/>
       <c r="M16" s="80"/>
       <c r="N16" s="80"/>
-      <c r="O16" s="80"/>
     </row>
     <row r="17" spans="1:15" ht="55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="88"/>
@@ -64990,28 +65231,25 @@
         <v>131</v>
       </c>
       <c r="H17" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="I17" s="86" t="s">
         <v>114</v>
       </c>
+      <c r="I17" s="87" t="s">
+        <v>112</v>
+      </c>
       <c r="J17" s="87" t="s">
-        <v>112</v>
-      </c>
-      <c r="K17" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="L17" s="86" t="s">
+      <c r="K17" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="M17" s="87" t="s">
+      <c r="L17" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="N17" s="86" t="s">
+      <c r="M17" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="O17" s="87" t="s">
-        <v>160</v>
+      <c r="N17" s="87" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
@@ -65020,7 +65258,7 @@
       </c>
       <c r="B18" s="90">
         <f>(E13*I6)*D13</f>
-        <v>542189999.99999988</v>
+        <v>728570000</v>
       </c>
       <c r="C18" s="90">
         <f>1896*L2</f>
@@ -65028,7 +65266,7 @@
       </c>
       <c r="D18" s="90">
         <f>E8*L4</f>
-        <v>345000000</v>
+        <v>495000000</v>
       </c>
       <c r="E18" s="90">
         <f>50*L6</f>
@@ -65036,443 +65274,58 @@
       </c>
       <c r="F18" s="90">
         <f>(F8-E8)*L3</f>
-        <v>807000000</v>
+        <v>747000000</v>
       </c>
       <c r="G18" s="90">
         <f>(E8)*L5</f>
-        <v>690000000</v>
-      </c>
-      <c r="H18" s="90">
-        <v>100000000</v>
-      </c>
-      <c r="I18" s="91" t="s">
+        <v>990000000</v>
+      </c>
+      <c r="H18" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="J18" s="90">
+      <c r="I18" s="90">
         <f ca="1">B8*I1</f>
         <v>0</v>
       </c>
-      <c r="K18" s="24">
+      <c r="J18" s="24">
         <f>E3</f>
-        <v>427000000</v>
-      </c>
-      <c r="L18" s="46">
-        <f ca="1">SUM(B18:K18)</f>
-        <v>3093070000</v>
-      </c>
-      <c r="M18" s="50">
+        <v>184000000</v>
+      </c>
+      <c r="K18" s="46">
+        <f ca="1">SUM(B18:J18)</f>
+        <v>3326450000</v>
+      </c>
+      <c r="L18" s="50">
         <f>F3</f>
-        <v>151663000</v>
-      </c>
-      <c r="N18" s="113">
-        <f ca="1">(L18-M18)/B3</f>
-        <v>1.0544876509886432</v>
-      </c>
-      <c r="O18" s="57">
+        <v>1056000000</v>
+      </c>
+      <c r="M18" s="113">
+        <f ca="1">(K18-L18)/B3</f>
+        <v>0.99461306358962698</v>
+      </c>
+      <c r="N18" s="57">
         <f ca="1">N21/D3</f>
-        <v>13.718884339362246</v>
+        <v>10.115214856706507</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="N21" s="114">
-        <f ca="1">L18-M18</f>
-        <v>2941407000</v>
+        <f ca="1">K18-L18</f>
+        <v>2270450000</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="O22" s="82"/>
     </row>
-    <row r="43" spans="1:23" ht="24" x14ac:dyDescent="0.3">
-      <c r="A43" s="72" t="s">
-        <v>162</v>
-      </c>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="128" t="s">
-        <v>161</v>
-      </c>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="H43" s="20" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I43" s="21" cm="1">
-        <f t="array" aca="1" ref="I43" ca="1">_FV(H43,"Price")</f>
-        <v>97857.13</v>
-      </c>
-      <c r="K43" s="81" t="s">
-        <v>111</v>
-      </c>
-      <c r="L43" s="79"/>
+    <row r="43" spans="4:23" x14ac:dyDescent="0.2">
+      <c r="D43" s="123"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A44" s="64"/>
-      <c r="B44" s="77" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="128"/>
-      <c r="E44" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="F44" s="77" t="s">
-        <v>71</v>
-      </c>
-      <c r="H44" s="45" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I44" s="21" cm="1">
-        <f t="array" aca="1" ref="I44" ca="1">_FV(H44,"Price")</f>
-        <v>2746.41</v>
-      </c>
-      <c r="K44" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="L44" s="90">
-        <v>30000</v>
-      </c>
+    <row r="44" spans="4:23" x14ac:dyDescent="0.2">
+      <c r="D44" s="123"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A45" s="60" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B45" s="28">
-        <f ca="1">C45*D45</f>
-        <v>3789418157.0000005</v>
-      </c>
-      <c r="C45" s="14" cm="1">
-        <f t="array" aca="1" ref="C45" ca="1">_FV(A45,"Price")</f>
-        <v>13.01</v>
-      </c>
-      <c r="D45" s="116" cm="1">
-        <f t="array" aca="1" ref="D45" ca="1">_FV(A45,"Shares outstanding",TRUE)+M52</f>
-        <v>291269650.80707151</v>
-      </c>
-      <c r="E45" s="117">
-        <v>1098590000</v>
-      </c>
-      <c r="F45" s="58">
-        <v>151663000</v>
-      </c>
-      <c r="K45" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="L45" s="90">
-        <v>300000</v>
-      </c>
+    <row r="45" spans="4:23" x14ac:dyDescent="0.2">
       <c r="W45" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B46" s="14"/>
-      <c r="K46" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="L46" s="90">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" ht="19" x14ac:dyDescent="0.25">
-      <c r="H47" s="81" t="s">
-        <v>101</v>
-      </c>
-      <c r="I47" s="81"/>
-      <c r="K47" s="93" t="s">
-        <v>143</v>
-      </c>
-      <c r="L47" s="90">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" ht="24" x14ac:dyDescent="0.3">
-      <c r="A48" s="70" t="s">
-        <v>88</v>
-      </c>
-      <c r="B48" s="70"/>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="I48" s="82">
-        <v>17.489999999999998</v>
-      </c>
-      <c r="K48" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="L48" s="90">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B49" s="77" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="77" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="F49" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="G49" s="77" t="s">
-        <v>147</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="I49" s="82">
-        <v>12.68</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A50" s="60" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50" s="24">
-        <f t="shared" ref="C50" si="1">B50*$M$3</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="74">
-        <f ca="1">C50/B45</f>
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <v>460</v>
-      </c>
-      <c r="F50">
-        <v>3150</v>
-      </c>
-      <c r="G50" s="16">
-        <v>2310</v>
-      </c>
-      <c r="H50" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="I50" s="82">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C51" s="24"/>
-      <c r="D51" s="74"/>
-      <c r="F51" s="78"/>
-      <c r="H51" s="123"/>
-      <c r="I51" s="82"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C52" s="24"/>
-      <c r="D52" s="74"/>
-      <c r="F52" s="78"/>
-      <c r="M52" s="115">
-        <f ca="1">1000000000/C45</f>
-        <v>76863950.807071492</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="24" x14ac:dyDescent="0.3">
-      <c r="A53" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="B53" s="73"/>
-      <c r="C53" s="73"/>
-      <c r="D53" s="73"/>
-      <c r="E53" s="73"/>
-      <c r="F53" s="73"/>
-      <c r="G53" s="73"/>
-      <c r="H53" s="73"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B54" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" s="77" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="77" t="s">
-        <v>86</v>
-      </c>
-      <c r="E54" s="85" t="s">
-        <v>105</v>
-      </c>
-      <c r="F54" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="G54" s="77" t="s">
-        <v>145</v>
-      </c>
-      <c r="H54" s="77" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A55" s="60" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B55" s="89">
-        <f>(E50*1000000)/(F55*1000000)</f>
-        <v>16.428571428571427</v>
-      </c>
-      <c r="C55" s="69">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1">
-        <v>76105</v>
-      </c>
-      <c r="E55" s="84">
-        <f>(F55*1000000)/D55</f>
-        <v>367.91275211878326</v>
-      </c>
-      <c r="F55">
-        <v>28</v>
-      </c>
-      <c r="G55">
-        <v>31</v>
-      </c>
-      <c r="H55">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="24" x14ac:dyDescent="0.3">
-      <c r="A58" s="80" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58" s="80"/>
-      <c r="C58" s="80"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="80"/>
-      <c r="F58" s="80"/>
-      <c r="G58" s="80"/>
-      <c r="H58" s="80"/>
-      <c r="I58" s="80"/>
-      <c r="J58" s="80"/>
-      <c r="K58" s="80"/>
-      <c r="L58" s="80"/>
-      <c r="M58" s="80"/>
-      <c r="N58" s="80"/>
-      <c r="O58" s="80"/>
-    </row>
-    <row r="59" spans="1:15" ht="53" x14ac:dyDescent="0.3">
-      <c r="A59" s="88"/>
-      <c r="B59" s="86" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" s="86" t="s">
-        <v>95</v>
-      </c>
-      <c r="D59" s="87" t="s">
-        <v>122</v>
-      </c>
-      <c r="E59" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="F59" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="G59" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="H59" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="I59" s="86" t="s">
-        <v>114</v>
-      </c>
-      <c r="J59" s="87" t="s">
-        <v>112</v>
-      </c>
-      <c r="K59" s="87" t="s">
-        <v>70</v>
-      </c>
-      <c r="L59" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="M59" s="87" t="s">
-        <v>99</v>
-      </c>
-      <c r="N59" s="86" t="s">
-        <v>100</v>
-      </c>
-      <c r="O59" s="87" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A60" s="60" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B60" s="90">
-        <f>(E55*I48)*D55</f>
-        <v>489720000</v>
-      </c>
-      <c r="C60" s="90">
-        <f>1896*L44</f>
-        <v>56880000</v>
-      </c>
-      <c r="D60" s="90">
-        <f>E50*L46</f>
-        <v>345000000</v>
-      </c>
-      <c r="E60" s="90">
-        <f>50*L48</f>
-        <v>125000000</v>
-      </c>
-      <c r="F60" s="90">
-        <f>(F50-E50)*L45</f>
-        <v>807000000</v>
-      </c>
-      <c r="G60" s="90">
-        <f>(E50)*L47</f>
-        <v>690000000</v>
-      </c>
-      <c r="H60" s="90">
-        <v>100000000</v>
-      </c>
-      <c r="I60" s="91" t="s">
-        <v>6</v>
-      </c>
-      <c r="J60" s="90">
-        <f ca="1">B50*I43</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="118">
-        <f>E45</f>
-        <v>1098590000</v>
-      </c>
-      <c r="L60" s="46">
-        <f ca="1">SUM(B60:K60)</f>
-        <v>3712190000</v>
-      </c>
-      <c r="M60" s="50">
-        <f>F45</f>
-        <v>151663000</v>
-      </c>
-      <c r="N60" s="66">
-        <f ca="1">(L60-M60)/B45</f>
-        <v>0.93959728182090929</v>
-      </c>
-      <c r="O60" s="66">
-        <f ca="1">O68/D45</f>
-        <v>12.22416063649003</v>
-      </c>
-    </row>
-    <row r="68" spans="15:15" x14ac:dyDescent="0.2">
-      <c r="O68" s="114">
-        <f ca="1">L60-M60</f>
-        <v>3560527000</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -65560,30 +65413,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8 H9">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G50 H51">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H6:H8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -65596,8 +65425,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H9 G8">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H48:H50">
     <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H51 G50">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -65632,7 +65485,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18">
+  <conditionalFormatting sqref="M18">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -65662,7 +65515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18:O18">
+  <conditionalFormatting sqref="M18:N18">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -65719,11 +65572,10 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="I18" r:id="rId1" xr:uid="{AF295A39-A2BD-D143-8662-676FC1FF04B4}"/>
-    <hyperlink ref="I60" r:id="rId2" xr:uid="{69C794A7-8F6A-1C44-9DA8-5BF294AC75D4}"/>
+    <hyperlink ref="H18" r:id="rId1" xr:uid="{AF295A39-A2BD-D143-8662-676FC1FF04B4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -65761,7 +65613,7 @@
       </c>
       <c r="I1" s="21" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_FV(H1,"Price")</f>
-        <v>97857.13</v>
+        <v>106293.72</v>
       </c>
       <c r="K1" s="81" t="s">
         <v>111</v>
@@ -65790,7 +65642,7 @@
       </c>
       <c r="I2" s="21" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">_FV(H2,"Price")</f>
-        <v>2746.41</v>
+        <v>2652.65</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>124</v>
@@ -65805,15 +65657,15 @@
       </c>
       <c r="B3" s="15" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A3,"Market cap",TRUE)</f>
-        <v>472808952</v>
+        <v>540230340</v>
       </c>
       <c r="C3" s="14" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Price")</f>
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="D3" s="1" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(A3,"Shares outstanding",TRUE)</f>
-        <v>153509400</v>
+        <v>207780900</v>
       </c>
       <c r="E3" s="48">
         <v>59000000</v>
@@ -65910,11 +65762,11 @@
       </c>
       <c r="D8" s="24">
         <f ca="1">C8*I1</f>
-        <v>57344278.18</v>
+        <v>62288119.920000002</v>
       </c>
       <c r="E8" s="74">
         <f ca="1">F9+B9</f>
-        <v>0.15815374212711605</v>
+        <v>0.1336905690080272</v>
       </c>
       <c r="F8" s="68">
         <v>75</v>
@@ -65932,11 +65784,11 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="74">
         <f ca="1">I18/B3</f>
-        <v>0.15815374212711605</v>
+        <v>0.1336905690080272</v>
       </c>
       <c r="C9" s="74">
         <f ca="1">$D$8/$B$3</f>
-        <v>0.12128424797675996</v>
+        <v>0.11529918871272576</v>
       </c>
       <c r="D9" s="74"/>
       <c r="F9" s="74"/>
@@ -66099,11 +65951,11 @@
       </c>
       <c r="I18" s="28">
         <f ca="1">B8*I2</f>
-        <v>74776505.069999993</v>
+        <v>72223701.549999997</v>
       </c>
       <c r="J18" s="90">
         <f ca="1">C8*I1</f>
-        <v>57344278.18</v>
+        <v>62288119.920000002</v>
       </c>
       <c r="K18" s="24">
         <f>E3</f>
@@ -66111,7 +65963,7 @@
       </c>
       <c r="L18" s="46">
         <f ca="1">SUM(B18:K18)</f>
-        <v>360460783.25</v>
+        <v>362851821.47000003</v>
       </c>
       <c r="M18" s="50">
         <f>F3</f>
@@ -66119,7 +65971,7 @@
       </c>
       <c r="N18" s="66">
         <f ca="1">(L18-M18)/B3</f>
-        <v>0.71962499612316988</v>
+        <v>0.63424090263053357</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="21" x14ac:dyDescent="0.25">
